--- a/02_Glider_Design/C_results/weight_sweep.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9f2c90c-dirty</t>
+          <t>93578c8</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-28T20:25:14.309978+00:00</t>
+          <t>2026-03-31T05:59:12.547037+00:00</t>
         </is>
       </c>
     </row>

--- a/02_Glider_Design/C_results/weight_sweep.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93578c8</t>
+          <t>914634d-dirty</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-31T05:59:12.547037+00:00</t>
+          <t>2026-04-01T06:29:01.679249+00:00</t>
         </is>
       </c>
     </row>

--- a/02_Glider_Design/C_results/weight_sweep.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>914634d-dirty</t>
+          <t>aadd597</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-01T06:29:01.679249+00:00</t>
+          <t>2026-04-02T00:29:37.625684+00:00</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>690864919</v>
+        <v>3476624471</v>
       </c>
     </row>
     <row r="7">
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AQ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,46 +1546,46 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9553165280177863</v>
+        <v>0.9553165269985133</v>
       </c>
       <c r="P3" t="n">
-        <v>1.026468194560592</v>
+        <v>1.026468193785818</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.69527831641379</v>
+        <v>10.69527831522339</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6837933699478116</v>
+        <v>0.6837933708686902</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09999999776980481</v>
+        <v>0.0999999975601196</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3999999946589768</v>
+        <v>0.3999999946291775</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2247878180912749</v>
+        <v>0.2247878180178422</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09999999867065287</v>
+        <v>0.09999999849367161</v>
       </c>
       <c r="W3" t="n">
-        <v>0.86761500621457</v>
+        <v>0.8676150055347496</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1005400514018585</v>
+        <v>0.1005400513964218</v>
       </c>
       <c r="Y3" t="n">
-        <v>93080.9989149614</v>
+        <v>93080.99799101072</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.026468194560592</v>
+        <v>1.026468193785818</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6837933699478116</v>
+        <v>0.6837933708686902</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.86761500621457</v>
+        <v>0.8676150055347496</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.110858935378161</v>
+        <v>9.110858934885488</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.788097508173309e-05</v>
+        <v>9.788097604803687e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.06404260227213419</v>
+        <v>0.06404260216535194</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.5142945688583989</v>
+        <v>0.5142945690508326</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1383693227154416</v>
+        <v>0.1383693226109227</v>
       </c>
       <c r="AK3" t="n">
-        <v>10.69527831641379</v>
+        <v>10.69527831522339</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1679,46 +1679,46 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7105799757302431</v>
+        <v>0.7105799744973521</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7387885464992657</v>
+        <v>0.7387885452279294</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.10563290288994</v>
+        <v>44.1056328937458</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7615699664985112</v>
+        <v>0.7615699665221116</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1759907663246253</v>
+        <v>0.1759907664401166</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3999999951571052</v>
+        <v>0.3999999946329323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3868597711273762</v>
+        <v>0.3868597710354115</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1227936943712875</v>
+        <v>0.1227936888800635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.673541910786955</v>
+        <v>0.6735419094468442</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1201050769025705</v>
+        <v>0.1201050768040382</v>
       </c>
       <c r="Y4" t="n">
-        <v>5505003.771614874</v>
+        <v>5505004.13222688</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7387885464992657</v>
+        <v>0.7387885452279294</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7615699664985112</v>
+        <v>0.7615699665221116</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.673541910786955</v>
+        <v>0.6735419094468442</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05036414577637307</v>
+        <v>0.05036414573505512</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.452069881140419e-06</v>
+        <v>7.452069391491187e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>41.02367280201561</v>
+        <v>41.02367279380043</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.310340842783494</v>
+        <v>2.310340843309099</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.04770574945761798</v>
+        <v>0.04770574938498475</v>
       </c>
       <c r="AK4" t="n">
-        <v>44.10563290288994</v>
+        <v>44.1056328937458</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1812,46 +1812,46 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7548305660599789</v>
+        <v>0.7548305658560153</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7838159010364553</v>
+        <v>0.7838159010178805</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.32414572777261</v>
+        <v>16.32414572823105</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7615699665268847</v>
+        <v>0.76156996647908</v>
       </c>
       <c r="S5" t="n">
-        <v>0.221707484811705</v>
+        <v>0.2217074847540164</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3999999949329423</v>
+        <v>0.3999999946274935</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5000000049993342</v>
+        <v>0.5000000049891441</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2250638487449679</v>
+        <v>0.2250638486564479</v>
       </c>
       <c r="W5" t="n">
-        <v>1.285224520739491</v>
+        <v>1.285224520541978</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1342029222334378</v>
+        <v>0.1342029222135707</v>
       </c>
       <c r="Y5" t="n">
-        <v>199.8967442703541</v>
+        <v>199.8967442689788</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7838159010364553</v>
+        <v>0.7838159010178805</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7615699665268847</v>
+        <v>0.76156996647908</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.285224520739491</v>
+        <v>1.285224520541978</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3320208666555277</v>
+        <v>0.3320208666063761</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2999256911381165</v>
+        <v>0.2999256916849148</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.05166453337515717</v>
+        <v>0.05166453337423658</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.32757201594097</v>
+        <v>10.32757201568589</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.027738099923354</v>
+        <v>4.027738100337651</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.32414572777261</v>
+        <v>16.32414572823105</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1945,46 +1945,46 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7065761983848023</v>
+        <v>0.7065761982381304</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.040282843866633</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1452436796411457</v>
+        <v>0.1452436575838593</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4000000107106358</v>
+        <v>0.3999999945778784</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3300424233801231</v>
+        <v>0.33004237700595</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1115526089673369</v>
+        <v>0.1115525974183797</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1132083999413169</v>
+        <v>0.1132083947735417</v>
       </c>
       <c r="Y6" t="n">
-        <v>1886.446417239759</v>
+        <v>1886.463531825207</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1992,28 +1992,28 @@
         </is>
       </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2986784091644568</v>
+        <v>0.2986783955302841</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003543336722753047</v>
+        <v>0.0003543304565691389</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01451836706531169</v>
+        <v>0.01451836688553901</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.05710802689966259</v>
+        <v>0.05710803621085173</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001192220493771426</v>
+        <v>0.00119222063763572</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.040282843866633</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2075,78 +2075,78 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8875683742703702</v>
+        <v>1.207600258108835</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9345272009634895</v>
+        <v>1.254822053318313</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.33751025132958</v>
+        <v>17.34488294368279</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5645967832243941</v>
+        <v>0.548756805999245</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1854900228541271</v>
+        <v>0.09999999749911866</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3999999948263271</v>
+        <v>0.3999999945010851</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3116554712320814</v>
+        <v>0.2093206498764432</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09999999951743914</v>
+        <v>0.0999999983466104</v>
       </c>
       <c r="W7" t="n">
-        <v>1.078291506409421</v>
+        <v>1.083333332534641</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1090149001151575</v>
+        <v>0.09580553530929255</v>
       </c>
       <c r="Y7" t="n">
-        <v>59432.56015200894</v>
+        <v>187251.4725871418</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9345272009634895</v>
+        <v>1.254822053318313</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5645967832243941</v>
+        <v>0.548756805999245</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>fragile</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.078291506409421</v>
+        <v>1.083333332534641</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.47228207721264</v>
+        <v>15.3551609524391</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0002939850148222505</v>
+        <v>8.200288489209732e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.60206422231271</v>
+        <v>0.6152334991039476</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1833041077279695</v>
+        <v>0.2893480222299764</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00127435265201832</v>
+        <v>0.001725134490235862</v>
       </c>
       <c r="AK7" t="n">
-        <v>19.33751025132958</v>
+        <v>17.34488294368279</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2211,46 +2211,46 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7390725071505684</v>
+        <v>0.7390725074981561</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7676144724716895</v>
+        <v>0.7676144729923614</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.6705713541396</v>
+        <v>37.67057135585014</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7615699665082061</v>
+        <v>0.7615699664662087</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2349397525246482</v>
+        <v>0.2349397526031426</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3999999949882931</v>
+        <v>0.3999999946587426</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5000000049967872</v>
+        <v>0.5000000049905983</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418761370367478</v>
+        <v>0.1418761393351866</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7015559878038733</v>
+        <v>0.7015559882841867</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1340653886441527</v>
+        <v>0.1340653887003637</v>
       </c>
       <c r="Y8" t="n">
-        <v>3678.972842648452</v>
+        <v>3678.973528443422</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7676144724716895</v>
+        <v>0.7676144729923614</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7615699665082061</v>
+        <v>0.7615699664662087</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7015559878038733</v>
+        <v>0.7015559882841867</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02821024186337899</v>
+        <v>0.02821024187520698</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.008491738617743085</v>
+        <v>0.008491737035385034</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.590008794880593</v>
+        <v>5.590008795693675</v>
       </c>
       <c r="AI8" t="n">
-        <v>31.24087576154591</v>
+        <v>31.24087576368417</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1014288294281043</v>
+        <v>0.1014288292775145</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.6705713541396</v>
+        <v>37.67057135585014</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2344,46 +2344,46 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7546223922952391</v>
+        <v>0.7546223939910041</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7836017686019915</v>
+        <v>0.7836017703770652</v>
       </c>
       <c r="Q9" t="n">
-        <v>85.37983044228079</v>
+        <v>85.37983043642463</v>
       </c>
       <c r="R9" t="n">
-        <v>0.761569966498479</v>
+        <v>0.7615699665135085</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2211534110509503</v>
+        <v>0.221153409266387</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3999999946541582</v>
+        <v>0.3999999945488382</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5000000049755062</v>
+        <v>0.5000000049871816</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2247824227681909</v>
+        <v>0.2247824310798964</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7165236376208832</v>
+        <v>0.7165236392341808</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1341034216630249</v>
+        <v>0.1341034216457866</v>
       </c>
       <c r="Y9" t="n">
-        <v>5657.382270155623</v>
+        <v>5657.382275324826</v>
       </c>
       <c r="Z9" t="n">
         <v>-1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7836017686019915</v>
+        <v>0.7836017703770652</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.761569966498479</v>
+        <v>0.7615699665135085</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2394,25 +2394,25 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.7165236376208832</v>
+        <v>0.7165236392341808</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.818977927131223</v>
+        <v>7.818977926126136</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.06466258713502092</v>
+        <v>0.0646625836237749</v>
       </c>
       <c r="AH9" t="n">
-        <v>35.79369554100376</v>
+        <v>35.7936955399092</v>
       </c>
       <c r="AI9" t="n">
-        <v>40.97872734150536</v>
+        <v>40.97872733965374</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007243407884540587</v>
+        <v>0.007243407877594924</v>
       </c>
       <c r="AK9" t="n">
-        <v>85.37983044228079</v>
+        <v>85.37983043642463</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2876,46 +2876,46 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7357586407148693</v>
+        <v>0.7357586399586251</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7642074681647113</v>
+        <v>0.7642074682229132</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8930335242382</v>
+        <v>1.893033522174167</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7615699663401325</v>
+        <v>0.7615699665243296</v>
       </c>
       <c r="S13" t="n">
-        <v>0.229080622592276</v>
+        <v>0.2290806239231595</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3999999951287438</v>
+        <v>0.3999999944869926</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4888755010685937</v>
+        <v>0.4888755039531917</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1400958547850184</v>
+        <v>0.1400958521853115</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6983477895215862</v>
+        <v>0.6983477893561235</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1326457296224885</v>
+        <v>0.1326457298936473</v>
       </c>
       <c r="Y13" t="n">
-        <v>36106.59114871662</v>
+        <v>36106.59192686519</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.7642074681647113</v>
+        <v>0.7642074682229132</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.7615699663401325</v>
+        <v>0.7615699665243296</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2926,25 +2926,25 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.6983477895215862</v>
+        <v>0.6983477893561235</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1683831464395537</v>
+        <v>0.168383146783768</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.363665113040281e-05</v>
+        <v>2.363665056897416e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1118125562697212</v>
+        <v>0.1118125562756852</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.06102749686590316</v>
+        <v>0.06102749649616496</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.853438898490305</v>
+        <v>0.8534388966118557</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8930335242382</v>
+        <v>1.893033522174167</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3009,46 +3009,46 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.739072505262335</v>
+        <v>0.739072506335564</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7676144722149196</v>
+        <v>0.7676144733305823</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.779167033274233</v>
+        <v>6.779167038804034</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7615699665210792</v>
+        <v>0.7615699657525096</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2349397524717255</v>
+        <v>0.2349397521222798</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3999999949271048</v>
+        <v>0.3999999948425383</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5000000049865141</v>
+        <v>0.5000000038259413</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418761359336703</v>
+        <v>0.1418761403960595</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7015559875578061</v>
+        <v>0.7015559889671873</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1340653886106055</v>
+        <v>0.1340653885591926</v>
       </c>
       <c r="Y14" t="n">
-        <v>2971.755939833909</v>
+        <v>2971.75640087489</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.7676144722149196</v>
+        <v>0.7676144733305823</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7615699665210792</v>
+        <v>0.7615699657525096</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3059,25 +3059,25 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.7015559875578061</v>
+        <v>0.7015559889671873</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.685505795983094</v>
+        <v>3.685505794569735</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001240177817626933</v>
+        <v>0.001240177624749026</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.06782580321082217</v>
+        <v>0.06782580328461946</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.320492243747978</v>
+        <v>2.320492249400389</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.002547024956906671</v>
+        <v>0.002547024957354649</v>
       </c>
       <c r="AK14" t="n">
-        <v>6.779167033274233</v>
+        <v>6.779167038804034</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3408,46 +3408,46 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7390725081793591</v>
+        <v>0.7390725066895405</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7676144735156291</v>
+        <v>0.7676144721589616</v>
       </c>
       <c r="Q17" t="n">
-        <v>85.18250996043773</v>
+        <v>85.1825099522608</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7615699659922412</v>
+        <v>0.7615699665247377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2349397521713513</v>
+        <v>0.2349397522953915</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3999999946769558</v>
+        <v>0.3999999944699103</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5000000049932772</v>
+        <v>0.5000000049999341</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418761411749425</v>
+        <v>0.1418761359611861</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7015559888163525</v>
+        <v>0.7015559875024263</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1340653886419998</v>
+        <v>0.134065388576728</v>
       </c>
       <c r="Y17" t="n">
-        <v>128610.7189529293</v>
+        <v>128610.7100841301</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.7676144735156291</v>
+        <v>0.7676144721589616</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.7615699659922412</v>
+        <v>0.7615699665247377</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3458,25 +3458,25 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.7015559888163525</v>
+        <v>0.7015559875024263</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1762029029409149</v>
+        <v>0.1762029028551278</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0006526974104977978</v>
+        <v>0.0006526974554540676</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.06691394008675774</v>
+        <v>0.06691394003060191</v>
       </c>
       <c r="AI17" t="n">
-        <v>83.94388322283699</v>
+        <v>83.94388321605254</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.293301208346222</v>
+        <v>0.2933012083646475</v>
       </c>
       <c r="AK17" t="n">
-        <v>85.18250996043773</v>
+        <v>85.1825099522608</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3541,46 +3541,46 @@
         <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.377103855530809</v>
+        <v>1.377103859023908</v>
       </c>
       <c r="P18" t="n">
-        <v>1.377103855530809</v>
+        <v>1.377103859023908</v>
       </c>
       <c r="Q18" t="n">
-        <v>93.83305640512151</v>
+        <v>93.83305639194438</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5491731252679101</v>
+        <v>0.5491731255894229</v>
       </c>
       <c r="S18" t="n">
-        <v>0.09999999770013378</v>
+        <v>0.0999999975003934</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3999999945007257</v>
+        <v>0.3999999945276524</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2087990148187849</v>
+        <v>0.208799015126044</v>
       </c>
       <c r="V18" t="n">
-        <v>0.09999999850053209</v>
+        <v>0.09999999836445793</v>
       </c>
       <c r="W18" t="n">
-        <v>1.083333332639759</v>
+        <v>1.083333332584748</v>
       </c>
       <c r="X18" t="n">
-        <v>0.09580882276984003</v>
+        <v>0.09580882276109781</v>
       </c>
       <c r="Y18" t="n">
-        <v>2375706.749248032</v>
+        <v>2375706.478017149</v>
       </c>
       <c r="Z18" t="n">
         <v>-0.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.377103855530809</v>
+        <v>1.377103859023908</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5491731252679101</v>
+        <v>0.5491731255894229</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3591,25 +3591,25 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.083333332639759</v>
+        <v>1.083333332584748</v>
       </c>
       <c r="AF18" t="n">
-        <v>85.47043539289116</v>
+        <v>85.4704353850923</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.597684580386221e-05</v>
+        <v>3.597684990800254e-05</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.625973223111042</v>
+        <v>6.625973218147726</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.6124940029689304</v>
+        <v>0.6124940019417454</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.04078447666481171</v>
+        <v>0.04078447732796903</v>
       </c>
       <c r="AK18" t="n">
-        <v>93.83305640512151</v>
+        <v>93.83305639194438</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3807,46 +3807,46 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7390725054576268</v>
+        <v>0.7390725055989464</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7676144724157506</v>
+        <v>0.7676144725445296</v>
       </c>
       <c r="Q20" t="n">
-        <v>47.10057330632729</v>
+        <v>47.10057330413135</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7615699665094972</v>
+        <v>0.7615699664906304</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2349397524075687</v>
+        <v>0.2349397521353086</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3999999949521494</v>
+        <v>0.39999999452381</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5000000049958261</v>
+        <v>0.5000000049919868</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418761369401592</v>
+        <v>0.1418761379278414</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7015559877620728</v>
+        <v>0.7015559879037846</v>
       </c>
       <c r="X20" t="n">
-        <v>0.134065388622472</v>
+        <v>0.134065388592613</v>
       </c>
       <c r="Y20" t="n">
-        <v>151045.0319816367</v>
+        <v>151045.0333605088</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.7676144724157506</v>
+        <v>0.7676144725445296</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7615699665094972</v>
+        <v>0.7615699664906304</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -3857,25 +3857,25 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.7015559877620728</v>
+        <v>0.7015559879037846</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.537058777437571</v>
+        <v>7.537058775758921</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.0002119067408185741</v>
+        <v>0.0002119067388810408</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.30057441920349</v>
+        <v>6.300574419162774</v>
       </c>
       <c r="AI20" t="n">
-        <v>32.00746044406593</v>
+        <v>32.00746044360343</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.5537117711174027</v>
+        <v>0.553711770963569</v>
       </c>
       <c r="AK20" t="n">
-        <v>47.10057330632729</v>
+        <v>47.10057330413135</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3940,46 +3940,46 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7088706980322411</v>
+        <v>0.7088706979372842</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7371458388682482</v>
+        <v>0.7371458387517306</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.511240241404352</v>
+        <v>8.511240240793912</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7615699665154569</v>
+        <v>0.7615699665206378</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1723659450380373</v>
+        <v>0.1723659449643951</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3999999952315003</v>
+        <v>0.3999999946667304</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3726819935005621</v>
+        <v>0.3726819935734484</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1215225391544397</v>
+        <v>0.1215225387248258</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6717220664622725</v>
+        <v>0.6717220663314228</v>
       </c>
       <c r="X21" t="n">
-        <v>0.119051978723851</v>
+        <v>0.1190519786978871</v>
       </c>
       <c r="Y21" t="n">
-        <v>1667.953897168576</v>
+        <v>1667.953888504739</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7371458388682482</v>
+        <v>0.7371458387517306</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.7615699665154569</v>
+        <v>0.7615699665206378</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -3990,25 +3990,25 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.6717220664622725</v>
+        <v>0.6717220663314228</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.09487604889633459</v>
+        <v>0.09487604887564317</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.004255610826443748</v>
+        <v>0.004255610848348133</v>
       </c>
       <c r="AH21" t="n">
-        <v>7.098162662799634</v>
+        <v>7.098162662465219</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.569280386505155</v>
+        <v>0.5692803863700776</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.07294346591451237</v>
+        <v>0.0729434659032015</v>
       </c>
       <c r="AK21" t="n">
-        <v>8.511240241404352</v>
+        <v>8.511240240793912</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4070,49 +4070,49 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.116916643982271</v>
+        <v>1.173976470596933</v>
       </c>
       <c r="P22" t="n">
-        <v>1.116916643982271</v>
+        <v>1.208494968548445</v>
       </c>
       <c r="Q22" t="n">
-        <v>71.63182999509672</v>
+        <v>71.6318299863678</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5396803948256202</v>
+        <v>0.5396803945935512</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1041913706454146</v>
+        <v>0.1041913706284078</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3999999946175527</v>
+        <v>0.3999999944889326</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2147740497291313</v>
+        <v>0.2147740496573812</v>
       </c>
       <c r="V22" t="n">
-        <v>0.09999999868185457</v>
+        <v>0.09999999835295273</v>
       </c>
       <c r="W22" t="n">
-        <v>1.083333332647454</v>
+        <v>1.083333332670561</v>
       </c>
       <c r="X22" t="n">
-        <v>0.09610130538160445</v>
+        <v>0.09610130536305043</v>
       </c>
       <c r="Y22" t="n">
-        <v>14995.33429312562</v>
+        <v>14995.33423602986</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.116916643982271</v>
+        <v>1.208494968548445</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.5396803948256202</v>
+        <v>0.5396803945935512</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4123,25 +4123,25 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.083333332647454</v>
+        <v>1.083333332670561</v>
       </c>
       <c r="AF22" t="n">
-        <v>62.12248026946046</v>
+        <v>62.12248025746664</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.004142787286705543</v>
+        <v>0.004142787301679653</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.03177035879404738</v>
+        <v>0.03177035881100493</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.377626308264126</v>
+        <v>8.377626311443349</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.01247693864392253</v>
+        <v>0.012476938674569</v>
       </c>
       <c r="AK22" t="n">
-        <v>71.63182999509672</v>
+        <v>71.6318299863678</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4206,46 +4206,46 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7546223981604554</v>
+        <v>0.7546223960902997</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7836017723516262</v>
+        <v>0.7836017723073553</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.84258198895077</v>
+        <v>13.84258198787505</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7615699665266402</v>
+        <v>0.7615699665266403</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2211534075275629</v>
+        <v>0.221153407348591</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3999999949274396</v>
+        <v>0.3999999944724446</v>
       </c>
       <c r="U23" t="n">
         <v>0.5000000049993008</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2247824400507569</v>
+        <v>0.2247824400876461</v>
       </c>
       <c r="W23" t="n">
-        <v>0.7165236410298945</v>
+        <v>0.716523640988932</v>
       </c>
       <c r="X23" t="n">
-        <v>0.134103421664493</v>
+        <v>0.134103421630077</v>
       </c>
       <c r="Y23" t="n">
-        <v>4205.870458417156</v>
+        <v>4205.870458855159</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.7836017723516262</v>
+        <v>0.7836017723073553</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.7615699665266402</v>
+        <v>0.7615699665266403</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4256,25 +4256,25 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.7165236410298945</v>
+        <v>0.716523640988932</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.794326687467172</v>
+        <v>2.794326686750043</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.05297670243887542</v>
+        <v>0.05297670244466143</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.182950241493409</v>
+        <v>1.182950241440008</v>
       </c>
       <c r="AI23" t="n">
-        <v>9.0936425855962</v>
+        <v>9.093642585326482</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.002162130925216017</v>
+        <v>0.002162130924926722</v>
       </c>
       <c r="AK23" t="n">
-        <v>13.84258198895077</v>
+        <v>13.84258198787505</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4339,46 +4339,46 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7390725053562719</v>
+        <v>0.7390725052006916</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7676144723112218</v>
+        <v>0.7676144721511918</v>
       </c>
       <c r="Q24" t="n">
-        <v>89.56807893159024</v>
+        <v>89.56807892912367</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7615699665130625</v>
+        <v>0.7615699665293749</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2349397522523493</v>
+        <v>0.234939752293592</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3999999945198811</v>
+        <v>0.399999994468919</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5000000049977361</v>
+        <v>0.5000000049999154</v>
       </c>
       <c r="V24" t="n">
-        <v>0.141876136711023</v>
+        <v>0.1418761359389731</v>
       </c>
       <c r="W24" t="n">
-        <v>0.701555987658412</v>
+        <v>0.7015559874952293</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1340653885862481</v>
+        <v>0.1340653885762132</v>
       </c>
       <c r="Y24" t="n">
-        <v>14961.10367806067</v>
+        <v>14961.10367694684</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7676144723112218</v>
+        <v>0.7676144721511918</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.7615699665130625</v>
+        <v>0.7615699665293749</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4389,25 +4389,25 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.701555987658412</v>
+        <v>0.7015559874952293</v>
       </c>
       <c r="AF24" t="n">
-        <v>12.47440429263879</v>
+        <v>12.47440429170507</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.005278912614357476</v>
+        <v>0.005278912661984389</v>
       </c>
       <c r="AH24" t="n">
-        <v>9.437743496186361</v>
+        <v>9.437743495804936</v>
       </c>
       <c r="AI24" t="n">
-        <v>66.94462166474021</v>
+        <v>66.94462166370408</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.004474577752101901</v>
+        <v>0.004474577752365772</v>
       </c>
       <c r="AK24" t="n">
-        <v>89.56807893159024</v>
+        <v>89.56807892912367</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4472,46 +4472,46 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7390727285798031</v>
+        <v>0.7390727277483335</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7676147026762665</v>
+        <v>0.7676147019429332</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.795203835367839</v>
+        <v>4.795203833683704</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7615699664626012</v>
+        <v>0.7615699665269895</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2349404015988005</v>
+        <v>0.2349404013063279</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3999999947920046</v>
+        <v>0.3999999944812534</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5000000048873966</v>
+        <v>0.5000000049949567</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1418763349545109</v>
+        <v>0.141876332006719</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7015561147298349</v>
+        <v>0.7015561139306694</v>
       </c>
       <c r="X25" t="n">
-        <v>0.134065498725992</v>
+        <v>0.1340654986167144</v>
       </c>
       <c r="Y25" t="n">
-        <v>625.2741001761691</v>
+        <v>625.2741003041619</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.7676147026762665</v>
+        <v>0.7676147019429332</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.7615699664626012</v>
+        <v>0.7615699665269895</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4522,25 +4522,25 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.7015561147298349</v>
+        <v>0.7015561139306694</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5927176454364584</v>
+        <v>0.5927176449533305</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.03369099880757416</v>
+        <v>0.03369099943938616</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.754178606724216</v>
+        <v>1.754178606264762</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.710255014260311</v>
+        <v>1.710255013687422</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.002805455409443604</v>
+        <v>0.002805455408134527</v>
       </c>
       <c r="AK25" t="n">
-        <v>4.795203835367839</v>
+        <v>4.795203833683704</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4605,46 +4605,46 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7160462502740501</v>
+        <v>0.7160462502732621</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7441708389128964</v>
+        <v>0.7441708389123862</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9958525711030659</v>
+        <v>0.9958525710399788</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7615699665135721</v>
+        <v>0.7615699665134632</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1903446412042836</v>
+        <v>0.1903446411346351</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3999999950073199</v>
+        <v>0.3999999945525278</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4143030475001391</v>
+        <v>0.4143030476252892</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1277030957826929</v>
+        <v>0.1277030958305501</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6790561623408625</v>
+        <v>0.6790561623385187</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1234254496527301</v>
+        <v>0.1234254496400189</v>
       </c>
       <c r="Y26" t="n">
-        <v>60375.98373047768</v>
+        <v>60375.98416061448</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7441708389128964</v>
+        <v>0.7441708389123862</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.7615699665135721</v>
+        <v>0.7615699665134632</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -4655,25 +4655,25 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6790561623408625</v>
+        <v>0.6790561623385187</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.1265951261626692</v>
+        <v>0.1265951261496316</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.124712377975013e-05</v>
+        <v>1.124712369958339e-05</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.05257026776540284</v>
+        <v>0.05257026776452781</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1277057214073432</v>
+        <v>0.1277057213625968</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.009914046303008354</v>
+        <v>0.009914046301004257</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.9958525711030659</v>
+        <v>0.9958525710399788</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4738,46 +4738,46 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7546223877737905</v>
+        <v>0.9743006074141732</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7836017639668705</v>
+        <v>1.016605511278507</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.30267536204242</v>
+        <v>52.07815659593885</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7615699660268189</v>
+        <v>0.5376908912402081</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2211534165392882</v>
+        <v>0.2914549654284875</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3999999954499101</v>
+        <v>0.3999999949854747</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5000000049781063</v>
+        <v>0.5000000049701842</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2247823993247946</v>
+        <v>0.1821898419872857</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7165236333922114</v>
+        <v>1.408895375723267</v>
       </c>
       <c r="X27" t="n">
-        <v>0.1341034217690416</v>
+        <v>0.1277744364956107</v>
       </c>
       <c r="Y27" t="n">
-        <v>336541.8002563521</v>
+        <v>8059.258117237057</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.7836017639668705</v>
+        <v>1.016605511278507</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.7615699660268189</v>
+        <v>0.5376908912402081</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -4788,25 +4788,25 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.7165236333922114</v>
+        <v>1.408895375723267</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.01759654012023427</v>
+        <v>0.0167660747837412</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.0001361766688069859</v>
+        <v>0.005845324102689949</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.1293394180320896</v>
+        <v>0.1966403057741112</v>
       </c>
       <c r="AI27" t="n">
-        <v>45.82914127321605</v>
+        <v>47.10897572248539</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.609938320613022</v>
+        <v>3.341033793069651</v>
       </c>
       <c r="AK27" t="n">
-        <v>49.30267536204242</v>
+        <v>52.07815659593885</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5137,46 +5137,46 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7068416314792689</v>
+        <v>0.7068416316115292</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7362941208846542</v>
       </c>
       <c r="Q30" t="n">
-        <v>15.08876454754024</v>
+        <v>15.08876454814784</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.7615699665223312</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1437270658663271</v>
+        <v>0.1437270659696543</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3999999949369086</v>
+        <v>0.3999999946869297</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3272833303301916</v>
+        <v>0.3272833305199696</v>
       </c>
       <c r="V30" t="n">
-        <v>0.110968669304937</v>
+        <v>0.1109686700249502</v>
       </c>
       <c r="W30" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6685628415435685</v>
       </c>
       <c r="X30" t="n">
-        <v>0.1128747143516319</v>
+        <v>0.1128747143828861</v>
       </c>
       <c r="Y30" t="n">
-        <v>449640.5474722028</v>
+        <v>449640.5812073005</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7362941208846542</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.7615699665223312</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5187,25 +5187,25 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6685628415435685</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0293812896330642</v>
+        <v>0.02938128964119966</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.06217304349942e-05</v>
+        <v>3.062172813939781e-05</v>
       </c>
       <c r="AH30" t="n">
-        <v>13.76877163733701</v>
+        <v>13.76877163817078</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.6204284576181448</v>
+        <v>0.6204284572027006</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.001589699861886491</v>
+        <v>0.001589699861456285</v>
       </c>
       <c r="AK30" t="n">
-        <v>15.08876454754024</v>
+        <v>15.08876454814784</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5270,46 +5270,46 @@
         <v>0.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.377111284083251</v>
+        <v>1.37711128055112</v>
       </c>
       <c r="P31" t="n">
-        <v>1.377111284083251</v>
+        <v>1.37711128055112</v>
       </c>
       <c r="Q31" t="n">
-        <v>75.73228764891769</v>
+        <v>75.73228763606222</v>
       </c>
       <c r="R31" t="n">
-        <v>0.5491727733395404</v>
+        <v>0.5491727738003297</v>
       </c>
       <c r="S31" t="n">
-        <v>0.09999999766163428</v>
+        <v>0.09999999748976168</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3999999949239358</v>
+        <v>0.3999999944689408</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2087996887362319</v>
+        <v>0.2087996885615724</v>
       </c>
       <c r="V31" t="n">
-        <v>0.09999999842577559</v>
+        <v>0.09999999832143</v>
       </c>
       <c r="W31" t="n">
-        <v>1.083333332640151</v>
+        <v>1.083333332640155</v>
       </c>
       <c r="X31" t="n">
-        <v>0.09580882459726055</v>
+        <v>0.09580882458046941</v>
       </c>
       <c r="Y31" t="n">
-        <v>3061.302104446599</v>
+        <v>3061.302248515653</v>
       </c>
       <c r="Z31" t="n">
         <v>-0.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.377111284083251</v>
+        <v>1.37711128055112</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.5491727733395404</v>
+        <v>0.5491727738003297</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -5320,25 +5320,25 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.083333332640151</v>
+        <v>1.083333332640155</v>
       </c>
       <c r="AF31" t="n">
-        <v>73.61812456293364</v>
+        <v>73.61812455003158</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0240479776419328</v>
+        <v>0.02404797650598764</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.1104232112752492</v>
+        <v>0.1104232111557526</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.8572880687983905</v>
+        <v>0.8572880696147496</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.03907049562832649</v>
+        <v>0.03907049611401094</v>
       </c>
       <c r="AK31" t="n">
-        <v>75.73228764891769</v>
+        <v>75.73228763606222</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5357,6 +5357,1336 @@
       </c>
       <c r="AQ31" t="n">
         <v>-0.3942868043165935</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0142314041583111</v>
+      </c>
+      <c r="D32" t="n">
+        <v>39.35426538755546</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.03278016308046416</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0623605046386688</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1499042989646502</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.711031742426107</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.7392208858526121</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.8082470201227105</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.7615699665122504</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.181722727947182</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.3999999946696183</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.3793919650641271</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.1247773397652625</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.6738765211842358</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1208456200857916</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5004.334916908269</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.7392208858526121</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.7615699665122504</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.6738765211842358</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.01719802860202618</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0001346585575052926</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.02005751061024933</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.08968499903072319</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.007295302137970861</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.8082470201227105</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-1.846752247623304</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.594991809983201</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>-1.484388890156322</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>-1.205090379036396</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-0.8241859122494257</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.2665249348337844</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.033641969154031</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.583593190474212</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.17333088184672</v>
+      </c>
+      <c r="G33" t="n">
+        <v>28.97718244313807</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.7390727277964448</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.7676147019904146</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>11.43253038286904</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.7615699665264654</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2349404012601182</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3999999944747179</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.5000000049994059</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.1418763322934327</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.7015561139733216</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.1340654986155913</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>846.0982872289621</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.7676147019904146</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.7615699665264654</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.7015561139733216</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.3573179828197928</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.01029734715140867</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.3634389629386464</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>8.712567787808911</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.287352188176962</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>11.43253038286904</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.5742621541640669</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.6056973470940679</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>-0.2338897842164331</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.9123990808656299</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.462056155155667</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.5652974705408319</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1216997119723725</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.292519509802471</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.41410247565891</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1478950836805903</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.7390725069083347</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.7676144723074687</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>21.99563472639039</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.7615699665137924</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.2349397523281666</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3999999945585361</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.5000000049954174</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.14187613658744</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.7015559876588854</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.1340653885963619</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>49441.76800014252</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.7676144723074687</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.7615699665137924</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.7015559876588854</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.7578682506059707</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.0003107711257540985</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>5.164255355542384</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>15.36507390067725</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.00657046078014133</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>21.99563472639039</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-0.2477229578135707</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-0.9147104496167491</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.918686501956921</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.158787605308757</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>-0.8300462625540099</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.693864711902439</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08512832103909282</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1540108718148722</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8.728509814050597</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.02172733661985029</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.7390725070812486</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.7676144740993488</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>19.07718017297988</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.7615699655965384</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2349397523017425</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.3999999947649425</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.5000000048246006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.1418761428230911</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7015559896777094</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.1340653886701297</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>42801.79845282505</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.7676144740993488</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.7615699655965384</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.7015559896777094</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>8.974155743064658</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.0002173827783864018</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.0959119203513549</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>9.304373867609902</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.0009652694978680744</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>19.07718017297988</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.825676930688628</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-1.069925931985848</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-0.8124486207054025</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.9409401045558599</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>-1.66299350709844</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.07229213335904415</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01535491077162441</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.139200080194249</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.039820963255991</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.2272683272143778</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.7390725056935503</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.767614472169123</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6.363047213743364</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.7615699665285379</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.2349397523316962</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.3999999945134864</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.5000000049904808</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.1418761359702409</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.7015559875143377</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.1340653885833304</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>113389.3701041092</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.767614472169123</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.7615699665285379</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.7015559875143377</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.09691872950298198</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.921014220234645e-05</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>4.446013326016613</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.108423224464795</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.01009673610243466</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>6.363047213743364</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-1.140908958924494</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-1.813752702926789</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.8536495534821502</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.01695856875694353</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>-0.6434610846202489</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5309351101535278</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4.294096206681875</v>
+      </c>
+      <c r="E37" t="n">
+        <v>32.7055649293984</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.09809496344017229</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.697579830259134</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.7358747056375252</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.7730510478240536</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>21.28918165408557</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.7615699665296781</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.116717986979682</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.3999999944794566</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.2711586613917518</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.09999999835909167</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.690131327348511</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.1068444176183016</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1669.623164218233</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.7730510478240536</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.7615699665296781</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.690131327348511</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.5672745263746249</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.01176269040526402</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>19.63926037415636</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.2080100426385982</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.1727426931622109</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>21.28918165408557</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-0.2749585542938906</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.6328717703198401</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.514621655183362</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-1.008353290339657</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.4309743057471738</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6550595789833755</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.02089847824734005</v>
+      </c>
+      <c r="E38" t="n">
+        <v>47.85126936187322</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.04053147485742305</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.108293596298611</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.8082604707876937</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.8539841775274932</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>30.37365007086882</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.7615699665277879</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.09999999750720043</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.3999999945913169</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.2356948212519741</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.09999999840901282</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.756242544027705</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.1033169421656713</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>139380.5042967549</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.8539841775274932</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.7615699665277879</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.756242544027705</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.6767875263689442</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.0002051742933903325</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>28.59729648147489</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.1010420797569419</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.2420762649469512</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>30.37365007086882</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-0.1837191982570747</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-1.679885336513072</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.679893462897504</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1.392207592883359</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.613661472582538</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.111363539224585</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4544755086935829</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20.64066698352675</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.283865809529155</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.390540257019912</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.7090726503138383</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.7393330330635456</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>13.79316506346238</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.7615699665294804</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.1367529893089015</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.3999999944841699</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.3144562634673821</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.1082429233208199</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.6699565458920295</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.1113427555013318</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>172457.8092714869</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.7393330330635456</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.7615699665294804</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.6699565458920295</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.1239952331964594</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>7.230738180348714e-05</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>12.46997265998637</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.5067553648956864</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.02241295211003408</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>13.79316506346238</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-0.9532569752794666</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-0.3424895155791332</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.314723726995144</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-0.5468869133107761</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>-0.4083341922592103</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.2617924037677132</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5063414494913574</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1939218787159543</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.08419230020946894</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6142627044519234</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.7074074207948957</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.7358349780667149</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.253673761603159</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.7615699665150848</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.1640097423980078</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.3999999945420345</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.364382396364976</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.1185402726381636</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.6701716475842225</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.1173831996417614</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11091.11787807762</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.7358349780667149</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.7615699665150848</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.6701716475842225</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.3073002999616207</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>6.04241749976226e-05</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.118111584264663</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.126734732613569</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.03129507300408594</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.253673761603159</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-0.5820429591971319</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-0.2955565194854586</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-0.7123731900467094</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-1.074727625002086</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-0.2116458524851494</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>19.35150856297827</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.06574519117329922</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.01893126805242537</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.15380173061912</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.01311229504247801</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.7321004961372648</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.7672267018745381</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>25.92109193242866</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.7444836183979575</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.1253845239831866</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.3999999944697921</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.2836501636736412</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.1013207517637418</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.6881603226577808</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.1079289272694921</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>260950.804436112</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.7672267018745381</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.7444836183979575</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.6881603226577808</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>20.88587560248636</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>8.003759807377717e-05</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.01168747177718339</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>4.334453605900245</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.0008348920090189685</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>25.92109193242866</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.28671482646292</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>-1.182136007450779</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>-1.72282029518956</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.3332057215890512</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>-1.882321287177146</v>
       </c>
     </row>
   </sheetData>
@@ -5370,7 +6700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AQ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5592,25 +6922,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="D2" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -5634,46 +6964,46 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7065761983848023</v>
+        <v>0.7074074207948957</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358349780667149</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.040282843866633</v>
+        <v>1.253673761603159</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665150848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1452436796411457</v>
+        <v>0.1640097423980078</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4000000107106358</v>
+        <v>0.3999999945420345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3300424233801231</v>
+        <v>0.364382396364976</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1115526089673369</v>
+        <v>0.1185402726381636</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6701716475842225</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1132083999413169</v>
+        <v>0.1173831996417614</v>
       </c>
       <c r="Y2" t="n">
-        <v>1886.446417239759</v>
+        <v>11091.11787807762</v>
       </c>
       <c r="Z2" t="n">
         <v>-1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358349780667149</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665150848</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -5684,66 +7014,66 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6701716475842225</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2986784091644568</v>
+        <v>0.3073002999616207</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0003543336722753047</v>
+        <v>6.04241749976226e-05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01451836706531169</v>
+        <v>0.118111584264663</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.05710802689966259</v>
+        <v>0.126734732613569</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001192220493771426</v>
+        <v>0.03129507300408594</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.040282843866633</v>
+        <v>1.253673761603159</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.5786748227286269</v>
+        <v>-0.5820429591971319</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.271343439133855</v>
+        <v>-0.2955565194854586</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1.620314140253805</v>
+        <v>-0.7123731900467094</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.470593513862387</v>
+        <v>-1.074727625002086</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.664399707010766</v>
+        <v>-0.2116458524851494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="E3" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -5767,46 +7097,46 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7075339758674855</v>
+        <v>0.7065761982381304</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7359454388140416</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.166267395066876</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="R3" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1646396706102183</v>
+        <v>0.1452436575838593</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3999999945860802</v>
+        <v>0.3999999945778784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3655521647927926</v>
+        <v>0.33004237700595</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1187676990613332</v>
+        <v>0.1115525974183797</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1175251467546148</v>
+        <v>0.1132083947735417</v>
       </c>
       <c r="Y3" t="n">
-        <v>760243.8491079494</v>
+        <v>1886.463531825207</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7359454388140416</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -5817,66 +7147,66 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0552234488683037</v>
+        <v>0.2986783955302841</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.72408364673732e-06</v>
+        <v>0.0003543304565691389</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.310723987779651</v>
+        <v>0.01451836688553901</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1174456015663288</v>
+        <v>0.05710803621085173</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01255907900548735</v>
+        <v>0.00119222063763572</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.166267395066876</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.328007276037948</v>
+        <v>-0.5786748227286269</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1.877483620203595</v>
+        <v>1.271343439133855</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.3327629351844993</v>
+        <v>-1.620314140253805</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.10618730434266</v>
+        <v>-1.470593513862387</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.6071740450757601</v>
+        <v>-1.664399707010766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.04698862362078716</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9334028457295769</v>
+        <v>0.01325917124942102</v>
       </c>
       <c r="E4" t="n">
-        <v>22.74354390023092</v>
+        <v>2.151606933843013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.0783091834800308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.2470733791131532</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -5900,46 +7230,46 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7068416314792689</v>
+        <v>0.7075339758674855</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7359454388140416</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.08876454754024</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1437270658663271</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3999999949369086</v>
+        <v>0.3999999945860802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3272833303301916</v>
+        <v>0.3655521647927926</v>
       </c>
       <c r="V4" t="n">
-        <v>0.110968669304937</v>
+        <v>0.1187676990613332</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1128747143516319</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="Y4" t="n">
-        <v>449640.5474722028</v>
+        <v>760243.8491079494</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7359454388140416</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -5950,66 +7280,66 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0293812896330642</v>
+        <v>0.0552234488683037</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.06217304349942e-05</v>
+        <v>1.72408364673732e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.76877163733701</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6204284576181448</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001589699861886491</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.08876454754024</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1.584525809905986</v>
+        <v>-1.328007276037948</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02993087938533014</v>
+        <v>-1.877483620203595</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.356858137414048</v>
+        <v>0.3327629351844993</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.4388288199215503</v>
+        <v>-1.10618730434266</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.5425210246808</v>
+        <v>-0.6071740450757601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07969296261459534</v>
+        <v>0.0260300013176861</v>
       </c>
       <c r="D5" t="n">
-        <v>68.02461780006593</v>
+        <v>0.9334028457295769</v>
       </c>
       <c r="E5" t="n">
-        <v>11.62825144079468</v>
+        <v>22.74354390023092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3879907805271877</v>
+        <v>0.3640585039483271</v>
       </c>
       <c r="G5" t="n">
-        <v>1.467194524883676</v>
+        <v>0.02867338561159859</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -6033,46 +7363,46 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7088706980322411</v>
+        <v>0.7068416316115292</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7371458388682482</v>
+        <v>0.7362941208846542</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.511240241404352</v>
+        <v>15.08876454814784</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7615699665154569</v>
+        <v>0.7615699665223312</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1723659450380373</v>
+        <v>0.1437270659696543</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3999999952315003</v>
+        <v>0.3999999946869297</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3726819935005621</v>
+        <v>0.3272833305199696</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1215225391544397</v>
+        <v>0.1109686700249502</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6717220664622725</v>
+        <v>0.6685628415435685</v>
       </c>
       <c r="X5" t="n">
-        <v>0.119051978723851</v>
+        <v>0.1128747143828861</v>
       </c>
       <c r="Y5" t="n">
-        <v>1667.953897168576</v>
+        <v>449640.5812073005</v>
       </c>
       <c r="Z5" t="n">
         <v>-1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7371458388682482</v>
+        <v>0.7362941208846542</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7615699665154569</v>
+        <v>0.7615699665223312</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -6083,66 +7413,66 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6717220664622725</v>
+        <v>0.6685628415435685</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09487604889633459</v>
+        <v>0.02938128964119966</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.004255610826443748</v>
+        <v>3.062172813939781e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.098162662799634</v>
+        <v>13.76877163817078</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.569280386505155</v>
+        <v>0.6204284572027006</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.07294346591451237</v>
+        <v>0.001589699861456285</v>
       </c>
       <c r="AK5" t="n">
-        <v>8.511240241404352</v>
+        <v>15.08876454814784</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1.098580027820818</v>
+        <v>-1.584525809905986</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.832666110351999</v>
+        <v>-0.02993087938533014</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.065514414065798</v>
+        <v>1.356858137414048</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.4111785940288324</v>
+        <v>-0.4388288199215503</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.1664876976762431</v>
+        <v>-1.5425210246808</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4485780739142275</v>
+        <v>0.07969296261459534</v>
       </c>
       <c r="D6" t="n">
-        <v>5.112700669023979</v>
+        <v>68.02461780006593</v>
       </c>
       <c r="E6" t="n">
-        <v>25.13734845172522</v>
+        <v>11.62825144079468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7665074838579709</v>
+        <v>0.3879907805271877</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9280640060000213</v>
+        <v>1.467194524883676</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -6166,46 +7496,46 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7102786034465864</v>
+        <v>0.7088706979372842</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7384985882281571</v>
+        <v>0.7371458387517306</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.70345521814231</v>
+        <v>8.511240240793912</v>
       </c>
       <c r="R6" t="n">
-        <v>0.761569966529568</v>
+        <v>0.7615699665206378</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1750511927742286</v>
+        <v>0.1723659449643951</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3999999945077114</v>
+        <v>0.3999999946667304</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3850805772435666</v>
+        <v>0.3726819935734484</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1224654649638185</v>
+        <v>0.1215225387248258</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6732312139436717</v>
+        <v>0.6717220663314228</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1198899447981875</v>
+        <v>0.1190519786978871</v>
       </c>
       <c r="Y6" t="n">
-        <v>8277.177029702643</v>
+        <v>1667.953888504739</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7384985882281571</v>
+        <v>0.7371458387517306</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.761569966529568</v>
+        <v>0.7615699665206378</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -6216,66 +7546,66 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6732312139436717</v>
+        <v>0.6717220663314228</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5378000051925401</v>
+        <v>0.09487604887564317</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001855927209509464</v>
+        <v>0.004255610848348133</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.36183806735186</v>
+        <v>7.098162662465219</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.083160740492317</v>
+        <v>0.5692803863700776</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0455692639524093</v>
+        <v>0.0729434659032015</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.70345521814231</v>
+        <v>8.511240240793912</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.3481619581511328</v>
+        <v>-1.098580027820818</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.7086503670280164</v>
+        <v>1.832666110351999</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.400319465334172</v>
+        <v>1.065514414065798</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.115483600519517</v>
+        <v>-0.4111785940288324</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.03242207066256111</v>
+        <v>0.1664876976762431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1614660078158535</v>
+        <v>0.4485780739142275</v>
       </c>
       <c r="D7" t="n">
-        <v>64.03576583533444</v>
+        <v>5.112700669023979</v>
       </c>
       <c r="E7" t="n">
-        <v>16.01114999347771</v>
+        <v>25.13734845172522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08411192924442622</v>
+        <v>0.7665074838579709</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4412529616002</v>
+        <v>0.9280640060000213</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -6299,46 +7629,46 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.708551172423629</v>
+        <v>0.7102786034465864</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7386418556746849</v>
+        <v>0.7384985882281571</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.76568038818848</v>
+        <v>17.70345521814231</v>
       </c>
       <c r="R7" t="n">
-        <v>0.761569966513444</v>
+        <v>0.761569966529568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1379522698723403</v>
+        <v>0.1750511927742286</v>
       </c>
       <c r="T7" t="n">
-        <v>0.39999999495088</v>
+        <v>0.3999999945077114</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3166851436462421</v>
+        <v>0.3850805772435666</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1087165158890231</v>
+        <v>0.1224654649638185</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6696105002604452</v>
+        <v>0.6732312139436717</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1116060735643416</v>
+        <v>0.1198899447981875</v>
       </c>
       <c r="Y7" t="n">
-        <v>1175.463927405984</v>
+        <v>8277.177029702643</v>
       </c>
       <c r="Z7" t="n">
         <v>-1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7386418556746849</v>
+        <v>0.7384985882281571</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.761569966513444</v>
+        <v>0.761569966529568</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -6349,66 +7679,66 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.6696105002604452</v>
+        <v>0.6732312139436717</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.180205871464367</v>
+        <v>0.5378000051925401</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.008232068335904725</v>
+        <v>0.001855927209509464</v>
       </c>
       <c r="AH7" t="n">
-        <v>9.676499376797011</v>
+        <v>15.36183806735186</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1489288073546014</v>
+        <v>1.083160740492317</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.08220376397614818</v>
+        <v>0.0455692639524093</v>
       </c>
       <c r="AK7" t="n">
-        <v>10.76568038818848</v>
+        <v>17.70345521814231</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.7919188923534559</v>
+        <v>-0.3481619581511328</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.806422607832782</v>
+        <v>0.7086503670280164</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.204422526040804</v>
+        <v>1.400319465334172</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1.07514240565721</v>
+        <v>-0.115483600519517</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1587402127262094</v>
+        <v>-0.03242207066256111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04193340287957067</v>
+        <v>0.1614660078158535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01916897279802344</v>
+        <v>64.03576583533444</v>
       </c>
       <c r="E8" t="n">
-        <v>67.10977843732265</v>
+        <v>16.01114999347771</v>
       </c>
       <c r="F8" t="n">
-        <v>1.643525161100753</v>
+        <v>0.08411192924442622</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9743393025583934</v>
+        <v>1.4412529616002</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -6432,46 +7762,46 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7105799757302431</v>
+        <v>0.708551172423629</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7387885464992657</v>
+        <v>0.7386418556746849</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.10563290288994</v>
+        <v>10.76568038818848</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7615699664985112</v>
+        <v>0.761569966513444</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1759907663246253</v>
+        <v>0.1379522698723403</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3999999951571052</v>
+        <v>0.39999999495088</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3868597711273762</v>
+        <v>0.3166851436462421</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1227936943712875</v>
+        <v>0.1087165158890231</v>
       </c>
       <c r="W8" t="n">
-        <v>0.673541910786955</v>
+        <v>0.6696105002604452</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1201050769025705</v>
+        <v>0.1116060735643416</v>
       </c>
       <c r="Y8" t="n">
-        <v>5505003.771614874</v>
+        <v>1175.463927405984</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7387885464992657</v>
+        <v>0.7386418556746849</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7615699664985112</v>
+        <v>0.761569966513444</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -6482,66 +7812,66 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.673541910786955</v>
+        <v>0.6696105002604452</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05036414577637307</v>
+        <v>0.180205871464367</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.452069881140419e-06</v>
+        <v>0.008232068335904725</v>
       </c>
       <c r="AH8" t="n">
-        <v>41.02367280201561</v>
+        <v>9.676499376797011</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.310340842783494</v>
+        <v>0.1489288073546014</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.04770574945761798</v>
+        <v>0.08220376397614818</v>
       </c>
       <c r="AK8" t="n">
-        <v>44.10563290288994</v>
+        <v>10.76568038818848</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1.377439893335641</v>
+        <v>-0.7919188923534559</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1.717401158906118</v>
+        <v>1.806422607832782</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.826785804997085</v>
+        <v>1.204422526040804</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.2157763571816047</v>
+        <v>-1.07514240565721</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.01128977867776102</v>
+        <v>0.1587402127262094</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1366974516130044</v>
+        <v>0.04193340287957067</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5891238804208955</v>
+        <v>0.01916897279802344</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1463900089913316</v>
+        <v>67.10977843732265</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03839637010854689</v>
+        <v>1.643525161100753</v>
       </c>
       <c r="G9" t="n">
-        <v>4.454483528366944</v>
+        <v>0.9743393025583934</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -6565,46 +7895,46 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7147569747822791</v>
+        <v>0.7105799744973521</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7428868686001313</v>
+        <v>0.7387885452279294</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.198075109181164</v>
+        <v>44.1056328937458</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7615699665186544</v>
+        <v>0.7615699665221116</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1872763351393943</v>
+        <v>0.1759907664401166</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3999999945853014</v>
+        <v>0.3999999946329323</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4084028784163257</v>
+        <v>0.3868597710354115</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1266696438481351</v>
+        <v>0.1227936888800635</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6777696706399496</v>
+        <v>0.6735419094468442</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1227105327254513</v>
+        <v>0.1201050768040382</v>
       </c>
       <c r="Y9" t="n">
-        <v>1541.580750929657</v>
+        <v>5505004.13222688</v>
       </c>
       <c r="Z9" t="n">
         <v>-1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7428868686001313</v>
+        <v>0.7387885452279294</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7615699665186544</v>
+        <v>0.7615699665221116</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -6615,66 +7945,66 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.6777696706399496</v>
+        <v>0.6735419094468442</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1677421710964337</v>
+        <v>0.05036414573505512</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0004396588827612292</v>
+        <v>7.452069391491187e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.08979927230118522</v>
+        <v>41.02367279380043</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.05077160315445976</v>
+        <v>2.310340843309099</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2115527331063742</v>
+        <v>0.04770574938498475</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.198075109181164</v>
+        <v>44.1056328937458</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.8642395817066926</v>
+        <v>-1.377439893335641</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.2297933725707151</v>
+        <v>-1.717401158906118</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.8344885625399088</v>
+        <v>1.826785804997085</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1.415709830745541</v>
+        <v>0.2157763571816047</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.6487973573553889</v>
+        <v>-0.01128977867776102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1025680899027367</v>
+        <v>0.0142314041583111</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01314027731349474</v>
+        <v>39.35426538755546</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08561783046005296</v>
+        <v>0.03278016308046416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09813881480770215</v>
+        <v>0.0623605046386688</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2102509186298785</v>
+        <v>0.1499042989646502</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -6698,46 +8028,46 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7160462502740501</v>
+        <v>0.711031742426107</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7441708389128964</v>
+        <v>0.7392208858526121</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9958525711030659</v>
+        <v>0.8082470201227105</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7615699665135721</v>
+        <v>0.7615699665122504</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1903446412042836</v>
+        <v>0.181722727947182</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3999999950073199</v>
+        <v>0.3999999946696183</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4143030475001391</v>
+        <v>0.3793919650641271</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1277030957826929</v>
+        <v>0.1247773397652625</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6790561623408625</v>
+        <v>0.6738765211842358</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1234254496527301</v>
+        <v>0.1208456200857916</v>
       </c>
       <c r="Y10" t="n">
-        <v>60375.98373047768</v>
+        <v>5004.334916908269</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7441708389128964</v>
+        <v>0.7392208858526121</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7615699665135721</v>
+        <v>0.7615699665122504</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -6748,66 +8078,66 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.6790561623408625</v>
+        <v>0.6738765211842358</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1265951261626692</v>
+        <v>0.01719802860202618</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.124712377975013e-05</v>
+        <v>0.0001346585575052926</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.05257026776540284</v>
+        <v>0.02005751061024933</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1277057214073432</v>
+        <v>0.08968499903072319</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.009914046303008354</v>
+        <v>0.007295302137970861</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9958525711030659</v>
+        <v>0.8082470201227105</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.9889877321548504</v>
+        <v>-1.846752247623304</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1.881395469293006</v>
+        <v>1.594991809983201</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1.067435781303917</v>
+        <v>-1.484388890156322</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1.008159191164386</v>
+        <v>-1.205090379036396</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.6772620980032222</v>
+        <v>-0.8241859122494257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1269420032735123</v>
+        <v>0.111363539224585</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01006386790887713</v>
+        <v>0.4544755086935829</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1798815067642112</v>
+        <v>20.64066698352675</v>
       </c>
       <c r="F11" t="n">
-        <v>0.055979382812861</v>
+        <v>0.283865809529155</v>
       </c>
       <c r="G11" t="n">
-        <v>19.13359420714474</v>
+        <v>0.390540257019912</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -6831,46 +8161,46 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7357586407148693</v>
+        <v>0.7090726503138383</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7642074681647113</v>
+        <v>0.7393330330635456</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8930335242382</v>
+        <v>13.79316506346238</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7615699663401325</v>
+        <v>0.7615699665294804</v>
       </c>
       <c r="S11" t="n">
-        <v>0.229080622592276</v>
+        <v>0.1367529893089015</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3999999951287438</v>
+        <v>0.3999999944841699</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4888755010685937</v>
+        <v>0.3144562634673821</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1400958547850184</v>
+        <v>0.1082429233208199</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6983477895215862</v>
+        <v>0.6699565458920295</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1326457296224885</v>
+        <v>0.1113427555013318</v>
       </c>
       <c r="Y11" t="n">
-        <v>36106.59114871662</v>
+        <v>172457.8092714869</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7642074681647113</v>
+        <v>0.7393330330635456</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7615699663401325</v>
+        <v>0.7615699665294804</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -6881,66 +8211,66 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.6983477895215862</v>
+        <v>0.6699565458920295</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1683831464395537</v>
+        <v>0.1239952331964594</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.363665113040281e-05</v>
+        <v>7.230738180348714e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1118125562697212</v>
+        <v>12.46997265998637</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.06102749686590316</v>
+        <v>0.5067553648956864</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.853438898490305</v>
+        <v>0.02241295211003408</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8930335242382</v>
+        <v>13.79316506346238</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.8963946523607476</v>
+        <v>-0.9532569752794666</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1.997235072099745</v>
+        <v>-0.3424895155791332</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.7450134832530741</v>
+        <v>1.314723726995144</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.251971894052178</v>
+        <v>-0.5468869133107761</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.281796559034639</v>
+        <v>-0.4083341922592103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4192286007618873</v>
+        <v>0.1366974516130044</v>
       </c>
       <c r="D12" t="n">
-        <v>11.88554469785207</v>
+        <v>0.5891238804208955</v>
       </c>
       <c r="E12" t="n">
-        <v>31.2471844884662</v>
+        <v>0.1463900089913316</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05565769332404687</v>
+        <v>0.03839637010854689</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1057202322313611</v>
+        <v>4.454483528366944</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -6964,46 +8294,46 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7312142914439073</v>
+        <v>0.7147569747822791</v>
       </c>
       <c r="P12" t="n">
-        <v>0.767348829518963</v>
+        <v>0.7428868686001313</v>
       </c>
       <c r="Q12" t="n">
-        <v>20.05719482474464</v>
+        <v>1.198075109181164</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7615699665273246</v>
+        <v>0.7615699665186544</v>
       </c>
       <c r="S12" t="n">
-        <v>0.11848763766677</v>
+        <v>0.1872763351393943</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3999999945898781</v>
+        <v>0.3999999945853014</v>
       </c>
       <c r="U12" t="n">
-        <v>0.276056214305906</v>
+        <v>0.4084028784163257</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1007552347646711</v>
+        <v>0.1266696438481351</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6863990969915308</v>
+        <v>0.6777696706399496</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1072628508425886</v>
+        <v>0.1227105327254513</v>
       </c>
       <c r="Y12" t="n">
-        <v>2794.27027713946</v>
+        <v>1541.580750929657</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.767348829518963</v>
+        <v>0.7428868686001313</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.7615699665273246</v>
+        <v>0.7615699665186544</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -7014,66 +8344,66 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.6863990969915308</v>
+        <v>0.6777696706399496</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4496765487246943</v>
+        <v>0.1677421710964337</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0246375128812872</v>
+        <v>0.0004396588827612292</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.77416698835574</v>
+        <v>0.08979927230118522</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.1155958692559484</v>
+        <v>0.05077160315445976</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.006718808535434577</v>
+        <v>0.2115527331063742</v>
       </c>
       <c r="AK12" t="n">
-        <v>20.05719482474464</v>
+        <v>1.198075109181164</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.3775490964218582</v>
+        <v>-0.8642395817066926</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.07501908962758</v>
+        <v>-0.2297933725707151</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.494810891561395</v>
+        <v>-0.8344885625399088</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1.254474796517903</v>
+        <v>-1.415709830745541</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.9758418915421445</v>
+        <v>0.6487973573553889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>5.979443423452179</v>
+        <v>0.1025680899027367</v>
       </c>
       <c r="D13" t="n">
-        <v>2.414382624731231</v>
+        <v>0.01314027731349474</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5057324072988556</v>
+        <v>0.08561783046005296</v>
       </c>
       <c r="F13" t="n">
-        <v>3.837698070070781</v>
+        <v>0.09813881480770215</v>
       </c>
       <c r="G13" t="n">
-        <v>8.760339571966979</v>
+        <v>0.2102509186298785</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -7097,46 +8427,46 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7390725007729315</v>
+        <v>0.7160462502732621</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7676144675941211</v>
+        <v>0.7441708389123862</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.51911735391436</v>
+        <v>0.9958525710399788</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7615699665259067</v>
+        <v>0.7615699665134632</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2349397445152191</v>
+        <v>0.1903446411346351</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3999999945017993</v>
+        <v>0.3999999945525278</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4999999902335595</v>
+        <v>0.4143030476252892</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1418761336159782</v>
+        <v>0.1277030958305501</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7015559831620772</v>
+        <v>0.6790561623385187</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1340653866871629</v>
+        <v>0.1234254496400189</v>
       </c>
       <c r="Y13" t="n">
-        <v>1300.230209145999</v>
+        <v>60375.98416061448</v>
       </c>
       <c r="Z13" t="n">
         <v>-1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.7676144675941211</v>
+        <v>0.7441708389123862</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.7615699665259067</v>
+        <v>0.7615699665134632</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -7147,66 +8477,66 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.7015559831620772</v>
+        <v>0.6790561623385187</v>
       </c>
       <c r="AF13" t="n">
-        <v>8.016363947391293</v>
+        <v>0.1265951261496316</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.006165342022515001</v>
+        <v>1.124712369958339e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3149502733253461</v>
+        <v>0.05257026776452781</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.090890589291493</v>
+        <v>0.1277057213625968</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.3891912187216326</v>
+        <v>0.009914046301004257</v>
       </c>
       <c r="AK13" t="n">
-        <v>13.51911735391436</v>
+        <v>0.9958525710399788</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.7766607610163558</v>
+        <v>-0.9889877321548504</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.3828060970129838</v>
+        <v>-1.881395469293006</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.2960792159143879</v>
+        <v>-1.067435781303917</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5840708037344662</v>
+        <v>-1.008159191164386</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.9425209407997248</v>
+        <v>-0.6772620980032222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2.74903599965513</v>
+        <v>0.1269420032735123</v>
       </c>
       <c r="D14" t="n">
-        <v>0.485660561432181</v>
+        <v>0.01006386790887713</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1089114998522537</v>
+        <v>0.1798815067642112</v>
       </c>
       <c r="F14" t="n">
-        <v>2.176872900881533</v>
+        <v>0.055979382812861</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0573312103389672</v>
+        <v>19.13359420714474</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -7230,46 +8560,46 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.739072505262335</v>
+        <v>0.7357586399586251</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7676144722149196</v>
+        <v>0.7642074682229132</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.779167033274233</v>
+        <v>1.893033522174167</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7615699665210792</v>
+        <v>0.7615699665243296</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2349397524717255</v>
+        <v>0.2290806239231595</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3999999949271048</v>
+        <v>0.3999999944869926</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5000000049865141</v>
+        <v>0.4888755039531917</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418761359336703</v>
+        <v>0.1400958521853115</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7015559875578061</v>
+        <v>0.6983477893561235</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1340653886106055</v>
+        <v>0.1326457298936473</v>
       </c>
       <c r="Y14" t="n">
-        <v>2971.755939833909</v>
+        <v>36106.59192686519</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.7676144722149196</v>
+        <v>0.7642074682229132</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7615699665210792</v>
+        <v>0.7615699665243296</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -7280,66 +8610,66 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.7015559875578061</v>
+        <v>0.6983477893561235</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.685505795983094</v>
+        <v>0.168383146783768</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001240177817626933</v>
+        <v>2.363665056897416e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.06782580321082217</v>
+        <v>0.1118125562756852</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.320492243747978</v>
+        <v>0.06102749649616496</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.002547024956906671</v>
+        <v>0.8534388966118557</v>
       </c>
       <c r="AK14" t="n">
-        <v>6.779167033274233</v>
+        <v>1.893033522174167</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4391804271294646</v>
+        <v>-0.8963946523607476</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.3136671624273255</v>
+        <v>-1.997235072099745</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.9629262611193901</v>
+        <v>-0.7450134832530741</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.3378330730203389</v>
+        <v>-1.251971894052178</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-1.241608889587855</v>
+        <v>1.281796559034639</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>9.304716470212332</v>
+        <v>19.35150856297827</v>
       </c>
       <c r="D15" t="n">
-        <v>2.067251685853676</v>
+        <v>0.06574519117329922</v>
       </c>
       <c r="E15" t="n">
-        <v>15.15468672317973</v>
+        <v>0.01893126805242537</v>
       </c>
       <c r="F15" t="n">
-        <v>62.8013013879274</v>
+        <v>2.15380173061912</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1007186669500895</v>
+        <v>0.01311229504247801</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -7363,46 +8693,46 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7390725053562719</v>
+        <v>0.7321004961372648</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7676144723112218</v>
+        <v>0.7672267018745381</v>
       </c>
       <c r="Q15" t="n">
-        <v>89.56807893159024</v>
+        <v>25.92109193242866</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7615699665130625</v>
+        <v>0.7444836183979575</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2349397522523493</v>
+        <v>0.1253845239831866</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3999999945198811</v>
+        <v>0.3999999944697921</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5000000049977361</v>
+        <v>0.2836501636736412</v>
       </c>
       <c r="V15" t="n">
-        <v>0.141876136711023</v>
+        <v>0.1013207517637418</v>
       </c>
       <c r="W15" t="n">
-        <v>0.701555987658412</v>
+        <v>0.6881603226577808</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1340653885862481</v>
+        <v>0.1079289272694921</v>
       </c>
       <c r="Y15" t="n">
-        <v>14961.10367806067</v>
+        <v>260950.804436112</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.7676144723112218</v>
+        <v>0.7672267018745381</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.7615699665130625</v>
+        <v>0.7444836183979575</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -7413,66 +8743,66 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.701555987658412</v>
+        <v>0.6881603226577808</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.47440429263879</v>
+        <v>20.88587560248636</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.005278912614357476</v>
+        <v>8.003759807377717e-05</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.437743496186361</v>
+        <v>0.01168747177718339</v>
       </c>
       <c r="AI15" t="n">
-        <v>66.94462166474021</v>
+        <v>4.334453605900245</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.004474577752101901</v>
+        <v>0.0008348920090189685</v>
       </c>
       <c r="AK15" t="n">
-        <v>89.56807893159024</v>
+        <v>25.92109193242866</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.9687031440118381</v>
+        <v>1.28671482646292</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.3153933547710808</v>
+        <v>-1.182136007450779</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.180546963085654</v>
+        <v>-1.72282029518956</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.797968643414579</v>
+        <v>0.3332057215890512</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.9968900309150017</v>
+        <v>-1.882321287177146</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>5.621927370577294</v>
+        <v>0.4192286007618873</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08298386460878653</v>
+        <v>11.88554469785207</v>
       </c>
       <c r="E16" t="n">
-        <v>10.11716747043071</v>
+        <v>31.2471844884662</v>
       </c>
       <c r="F16" t="n">
-        <v>30.02646246928498</v>
+        <v>0.05565769332404687</v>
       </c>
       <c r="G16" t="n">
-        <v>12.46354729854967</v>
+        <v>0.1057202322313611</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -7496,46 +8826,46 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7390725054576268</v>
+        <v>0.7312142914439073</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7676144724157506</v>
+        <v>0.767348829518963</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.10057330632729</v>
+        <v>20.05719482474464</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7615699665094972</v>
+        <v>0.7615699665273246</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2349397524075687</v>
+        <v>0.11848763766677</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3999999949521494</v>
+        <v>0.3999999945898781</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5000000049958261</v>
+        <v>0.276056214305906</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418761369401592</v>
+        <v>0.1007552347646711</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7015559877620728</v>
+        <v>0.6863990969915308</v>
       </c>
       <c r="X16" t="n">
-        <v>0.134065388622472</v>
+        <v>0.1072628508425886</v>
       </c>
       <c r="Y16" t="n">
-        <v>151045.0319816367</v>
+        <v>2794.27027713946</v>
       </c>
       <c r="Z16" t="n">
         <v>-1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.7676144724157506</v>
+        <v>0.767348829518963</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.7615699665094972</v>
+        <v>0.7615699665273246</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -7546,66 +8876,66 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.7015559877620728</v>
+        <v>0.6863990969915308</v>
       </c>
       <c r="AF16" t="n">
-        <v>7.537058777437571</v>
+        <v>0.4496765487246943</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0002119067408185741</v>
+        <v>0.0246375128812872</v>
       </c>
       <c r="AH16" t="n">
-        <v>6.30057441920349</v>
+        <v>18.77416698835574</v>
       </c>
       <c r="AI16" t="n">
-        <v>32.00746044406593</v>
+        <v>0.1155958692559484</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.5537117711174027</v>
+        <v>0.006718808535434577</v>
       </c>
       <c r="AK16" t="n">
-        <v>47.10057330632729</v>
+        <v>20.05719482474464</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.7498852306771044</v>
+        <v>-0.3775490964218582</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1.081006343679273</v>
+        <v>1.07501908962758</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.00505893897116</v>
+        <v>1.494810891561395</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.477504169342972</v>
+        <v>-1.254474796517903</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.095641666153879</v>
+        <v>-0.9758418915421445</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02104215125818708</v>
+        <v>5.979443423452179</v>
       </c>
       <c r="D17" t="n">
-        <v>3.325412447810311</v>
+        <v>2.414382624731231</v>
       </c>
       <c r="E17" t="n">
-        <v>8.976174452427511</v>
+        <v>0.5057324072988556</v>
       </c>
       <c r="F17" t="n">
-        <v>29.30732305942135</v>
+        <v>3.837698070070781</v>
       </c>
       <c r="G17" t="n">
-        <v>2.283070505697305</v>
+        <v>8.760339571966979</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -7629,46 +8959,46 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7390725071505684</v>
+        <v>0.7390725007729315</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7676144724716895</v>
+        <v>0.7676144675941211</v>
       </c>
       <c r="Q17" t="n">
-        <v>37.6705713541396</v>
+        <v>13.51911735391436</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7615699665082061</v>
+        <v>0.7615699665259067</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2349397525246482</v>
+        <v>0.2349397445152191</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3999999949882931</v>
+        <v>0.3999999945017993</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5000000049967872</v>
+        <v>0.4999999902335595</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418761370367478</v>
+        <v>0.1418761336159782</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7015559878038733</v>
+        <v>0.7015559831620772</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1340653886441527</v>
+        <v>0.1340653866871629</v>
       </c>
       <c r="Y17" t="n">
-        <v>3678.972842648452</v>
+        <v>1300.230209145999</v>
       </c>
       <c r="Z17" t="n">
         <v>-1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.7676144724716895</v>
+        <v>0.7676144675941211</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.7615699665082061</v>
+        <v>0.7615699665259067</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -7679,66 +9009,66 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.7015559878038733</v>
+        <v>0.7015559831620772</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02821024186337899</v>
+        <v>8.016363947391293</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.008491738617743085</v>
+        <v>0.006165342022515001</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.590008794880593</v>
+        <v>0.3149502733253461</v>
       </c>
       <c r="AI17" t="n">
-        <v>31.24087576154591</v>
+        <v>4.090890589291493</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1014288294281043</v>
+        <v>0.3891912187216326</v>
       </c>
       <c r="AK17" t="n">
-        <v>37.6705713541396</v>
+        <v>13.51911735391436</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1.676909861866215</v>
+        <v>0.7766607610163558</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.5218455181201316</v>
+        <v>0.3828060970129838</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.9530912845304442</v>
+        <v>-0.2960792159143879</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.466976151648421</v>
+        <v>0.5840708037344662</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.358519323563153</v>
+        <v>0.9425209407997248</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1314305688632557</v>
+        <v>9.304716470212332</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2555999695376994</v>
+        <v>2.067251685853676</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1074472726474269</v>
+        <v>15.15468672317973</v>
       </c>
       <c r="F18" t="n">
-        <v>78.74844877016187</v>
+        <v>62.8013013879274</v>
       </c>
       <c r="G18" t="n">
-        <v>6.601942877321682</v>
+        <v>0.1007186669500895</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -7762,46 +9092,46 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7390725081793591</v>
+        <v>0.7390725052006916</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7676144735156291</v>
+        <v>0.7676144721511918</v>
       </c>
       <c r="Q18" t="n">
-        <v>85.18250996043773</v>
+        <v>89.56807892912367</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7615699659922412</v>
+        <v>0.7615699665293749</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2349397521713513</v>
+        <v>0.234939752293592</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3999999946769558</v>
+        <v>0.399999994468919</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5000000049932772</v>
+        <v>0.5000000049999154</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418761411749425</v>
+        <v>0.1418761359389731</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7015559888163525</v>
+        <v>0.7015559874952293</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1340653886419998</v>
+        <v>0.1340653885762132</v>
       </c>
       <c r="Y18" t="n">
-        <v>128610.7189529293</v>
+        <v>14961.10367694684</v>
       </c>
       <c r="Z18" t="n">
         <v>-1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.7676144735156291</v>
+        <v>0.7676144721511918</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7615699659922412</v>
+        <v>0.7615699665293749</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -7812,66 +9142,66 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.7015559888163525</v>
+        <v>0.7015559874952293</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1762029029409149</v>
+        <v>12.47440429170507</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0006526974104977978</v>
+        <v>0.005278912661984389</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.06691394008675774</v>
+        <v>9.437743495804936</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.94388322283699</v>
+        <v>66.94462166370408</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.293301208346222</v>
+        <v>0.004474577752365772</v>
       </c>
       <c r="AK18" t="n">
-        <v>85.18250996043773</v>
+        <v>89.56807892912367</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.8813036123666507</v>
+        <v>0.9687031440118381</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.5924392022726743</v>
+        <v>0.3153933547710808</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.968804603804045</v>
+        <v>1.180546963085654</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.896242007576633</v>
+        <v>1.797968643414579</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.8196717623191474</v>
+        <v>-0.9968900309150017</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4421104990239706</v>
+        <v>0.1314305688632557</v>
       </c>
       <c r="D19" t="n">
-        <v>13.19732425925125</v>
+        <v>0.2555999695376994</v>
       </c>
       <c r="E19" t="n">
-        <v>2.816777489164546</v>
+        <v>0.1074472726474269</v>
       </c>
       <c r="F19" t="n">
-        <v>1.604404173315737</v>
+        <v>78.74844877016187</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06314837069594158</v>
+        <v>6.601942877321682</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -7895,46 +9225,46 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7390727285798031</v>
+        <v>0.7390725066895405</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7676147026762665</v>
+        <v>0.7676144721589616</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.795203835367839</v>
+        <v>85.1825099522608</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7615699664626012</v>
+        <v>0.7615699665247377</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2349404015988005</v>
+        <v>0.2349397522953915</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3999999947920046</v>
+        <v>0.3999999944699103</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5000000048873966</v>
+        <v>0.5000000049999341</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418763349545109</v>
+        <v>0.1418761359611861</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7015561147298349</v>
+        <v>0.7015559875024263</v>
       </c>
       <c r="X19" t="n">
-        <v>0.134065498725992</v>
+        <v>0.134065388576728</v>
       </c>
       <c r="Y19" t="n">
-        <v>625.2741001761691</v>
+        <v>128610.7100841301</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.7676147026762665</v>
+        <v>0.7676144721589616</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.7615699664626012</v>
+        <v>0.7615699665247377</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -7945,66 +9275,66 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.7015561147298349</v>
+        <v>0.7015559875024263</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5927176454364584</v>
+        <v>0.1762029028551278</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.03369099880757416</v>
+        <v>0.0006526974554540676</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.754178606724216</v>
+        <v>0.06691394003060191</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.710255014260311</v>
+        <v>83.94388321605254</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.002805455409443604</v>
+        <v>0.2933012083646475</v>
       </c>
       <c r="AK19" t="n">
-        <v>4.795203835367839</v>
+        <v>85.1825099522608</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.3544691715586477</v>
+        <v>-0.8813036123666507</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.120485887475754</v>
+        <v>-0.5924392022726743</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.4497525413255881</v>
+        <v>-0.968804603804045</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.2053137829815355</v>
+        <v>1.896242007576633</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-1.19963785028506</v>
+        <v>0.8196717623191474</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01312161903708897</v>
+        <v>0.07229213335904415</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07449348227690349</v>
+        <v>0.01535491077162441</v>
       </c>
       <c r="E20" t="n">
-        <v>0.20763873910875</v>
+        <v>7.139200080194249</v>
       </c>
       <c r="F20" t="n">
-        <v>42.99128608307436</v>
+        <v>1.039820963255991</v>
       </c>
       <c r="G20" t="n">
-        <v>59.22118257248598</v>
+        <v>0.2272683272143778</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -8028,46 +9358,46 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7546223877737905</v>
+        <v>0.7390725056935503</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7836017639668705</v>
+        <v>0.767614472169123</v>
       </c>
       <c r="Q20" t="n">
-        <v>49.30267536204242</v>
+        <v>6.363047213743364</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7615699660268189</v>
+        <v>0.7615699665285379</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2211534165392882</v>
+        <v>0.2349397523316962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3999999954499101</v>
+        <v>0.3999999945134864</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5000000049781063</v>
+        <v>0.5000000049904808</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2247823993247946</v>
+        <v>0.1418761359702409</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7165236333922114</v>
+        <v>0.7015559875143377</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1341034217690416</v>
+        <v>0.1340653885833304</v>
       </c>
       <c r="Y20" t="n">
-        <v>336541.8002563521</v>
+        <v>113389.3701041092</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.7836017639668705</v>
+        <v>0.767614472169123</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7615699660268189</v>
+        <v>0.7615699665285379</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -8078,66 +9408,66 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.7165236333922114</v>
+        <v>0.7015559875143377</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01759654012023427</v>
+        <v>0.09691872950298198</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.0001361766688069859</v>
+        <v>3.921014220234645e-05</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1293394180320896</v>
+        <v>4.446013326016613</v>
       </c>
       <c r="AI20" t="n">
-        <v>45.82914127321605</v>
+        <v>1.108423224464795</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.609938320613022</v>
+        <v>0.01009673610243466</v>
       </c>
       <c r="AK20" t="n">
-        <v>49.30267536204242</v>
+        <v>6.363047213743364</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1.882012575364866</v>
+        <v>-1.140908958924494</v>
       </c>
       <c r="AN20" t="n">
-        <v>-1.127881723694692</v>
+        <v>-1.813752702926789</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.6826916170488944</v>
+        <v>0.8536495534821502</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.633380437218148</v>
+        <v>0.01695856875694353</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.772477075454112</v>
+        <v>-0.6434610846202489</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>5.830558109679524</v>
+        <v>0.5652974705408319</v>
       </c>
       <c r="D21" t="n">
-        <v>35.37274159751259</v>
+        <v>0.1216997119723725</v>
       </c>
       <c r="E21" t="n">
-        <v>57.4624343358206</v>
+        <v>8.292519509802471</v>
       </c>
       <c r="F21" t="n">
-        <v>38.44122193197017</v>
+        <v>14.41410247565891</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1643575937684162</v>
+        <v>0.1478950836805903</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -8161,46 +9491,46 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7546223922952391</v>
+        <v>0.7390725069083347</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7836017686019915</v>
+        <v>0.7676144723074687</v>
       </c>
       <c r="Q21" t="n">
-        <v>85.37983044228079</v>
+        <v>21.99563472639039</v>
       </c>
       <c r="R21" t="n">
-        <v>0.761569966498479</v>
+        <v>0.7615699665137924</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2211534110509503</v>
+        <v>0.2349397523281666</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3999999946541582</v>
+        <v>0.3999999945585361</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5000000049755062</v>
+        <v>0.5000000049954174</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2247824227681909</v>
+        <v>0.14187613658744</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7165236376208832</v>
+        <v>0.7015559876588854</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1341034216630249</v>
+        <v>0.1340653885963619</v>
       </c>
       <c r="Y21" t="n">
-        <v>5657.382270155623</v>
+        <v>49441.76800014252</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7836017686019915</v>
+        <v>0.7676144723074687</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.761569966498479</v>
+        <v>0.7615699665137924</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -8211,66 +9541,66 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.7165236376208832</v>
+        <v>0.7015559876588854</v>
       </c>
       <c r="AF21" t="n">
-        <v>7.818977927131223</v>
+        <v>0.7578682506059707</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.06466258713502092</v>
+        <v>0.0003107711257540985</v>
       </c>
       <c r="AH21" t="n">
-        <v>35.79369554100376</v>
+        <v>5.164255355542384</v>
       </c>
       <c r="AI21" t="n">
-        <v>40.97872734150536</v>
+        <v>15.36507390067725</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.007243407884540587</v>
+        <v>0.00657046078014133</v>
       </c>
       <c r="AK21" t="n">
-        <v>85.37983044228079</v>
+        <v>21.99563472639039</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.7657101280614271</v>
+        <v>-0.2477229578135707</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.548668721520392</v>
+        <v>-0.9147104496167491</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.75938402047632</v>
+        <v>0.918686501956921</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.584797184144205</v>
+        <v>1.158787605308757</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.784210225531051</v>
+        <v>-0.8300462625540099</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2.083710208720972</v>
+        <v>5.621927370577294</v>
       </c>
       <c r="D22" t="n">
-        <v>28.98014922862266</v>
+        <v>0.08298386460878653</v>
       </c>
       <c r="E22" t="n">
-        <v>1.899083052130609</v>
+        <v>10.11716747043071</v>
       </c>
       <c r="F22" t="n">
-        <v>8.530541466329396</v>
+        <v>30.02646246928498</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04906014442553373</v>
+        <v>12.46354729854967</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -8294,46 +9624,46 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7546223981604554</v>
+        <v>0.7390725055989464</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7836017723516262</v>
+        <v>0.7676144725445296</v>
       </c>
       <c r="Q22" t="n">
-        <v>13.84258198895077</v>
+        <v>47.10057330413135</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7615699665266402</v>
+        <v>0.7615699664906304</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2211534075275629</v>
+        <v>0.2349397521353086</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3999999949274396</v>
+        <v>0.39999999452381</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5000000049993008</v>
+        <v>0.5000000049919868</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2247824400507569</v>
+        <v>0.1418761379278414</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7165236410298945</v>
+        <v>0.7015559879037846</v>
       </c>
       <c r="X22" t="n">
-        <v>0.134103421664493</v>
+        <v>0.134065388592613</v>
       </c>
       <c r="Y22" t="n">
-        <v>4205.870458417156</v>
+        <v>151045.0333605088</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7836017723516262</v>
+        <v>0.7676144725445296</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.7615699665266402</v>
+        <v>0.7615699664906304</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -8344,66 +9674,66 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.7165236410298945</v>
+        <v>0.7015559879037846</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.794326687467172</v>
+        <v>7.537058775758921</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.05297670243887542</v>
+        <v>0.0002119067388810408</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.182950241493409</v>
+        <v>6.300574419162774</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.0936425855962</v>
+        <v>32.00746044360343</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002162130925216017</v>
+        <v>0.553711770963569</v>
       </c>
       <c r="AK22" t="n">
-        <v>13.84258198895077</v>
+        <v>47.10057330413135</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.3188373194717369</v>
+        <v>0.7498852306771044</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.462100617470577</v>
+        <v>-1.081006343679273</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.2785439580457707</v>
+        <v>1.00505893897116</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.9309765983862466</v>
+        <v>1.477504169342972</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-1.309271177631467</v>
+        <v>1.095641666153879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2474021140001688</v>
+        <v>0.02104215125818708</v>
       </c>
       <c r="D23" t="n">
-        <v>29.59051462765532</v>
+        <v>3.325412447810311</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07579834580915878</v>
+        <v>8.976174452427511</v>
       </c>
       <c r="F23" t="n">
-        <v>9.156619574847772</v>
+        <v>29.30732305942135</v>
       </c>
       <c r="G23" t="n">
-        <v>76.28118375658613</v>
+        <v>2.283070505697305</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -8427,46 +9757,46 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7548305660599789</v>
+        <v>0.7390725074981561</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7838159010364553</v>
+        <v>0.7676144729923614</v>
       </c>
       <c r="Q23" t="n">
-        <v>16.32414572777261</v>
+        <v>37.67057135585014</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7615699665268847</v>
+        <v>0.7615699664662087</v>
       </c>
       <c r="S23" t="n">
-        <v>0.221707484811705</v>
+        <v>0.2349397526031426</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3999999949329423</v>
+        <v>0.3999999946587426</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5000000049993342</v>
+        <v>0.5000000049905983</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2250638487449679</v>
+        <v>0.1418761393351866</v>
       </c>
       <c r="W23" t="n">
-        <v>1.285224520739491</v>
+        <v>0.7015559882841867</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1342029222334378</v>
+        <v>0.1340653887003637</v>
       </c>
       <c r="Y23" t="n">
-        <v>199.8967442703541</v>
+        <v>3678.973528443422</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.7838159010364553</v>
+        <v>0.7676144729923614</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.7615699665268847</v>
+        <v>0.7615699664662087</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -8477,66 +9807,66 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.285224520739491</v>
+        <v>0.7015559882841867</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.3320208666555277</v>
+        <v>0.02821024187520698</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2999256911381165</v>
+        <v>0.008491737035385034</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.05166453337515717</v>
+        <v>5.590008795693675</v>
       </c>
       <c r="AI23" t="n">
-        <v>10.32757201594097</v>
+        <v>31.24087576368417</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.027738099923354</v>
+        <v>0.1014288292775145</v>
       </c>
       <c r="AK23" t="n">
-        <v>16.32414572777261</v>
+        <v>37.67057135585014</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.6065965937340381</v>
+        <v>-1.676909861866215</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.471152518320735</v>
+        <v>0.5218455181201316</v>
       </c>
       <c r="AO23" t="n">
-        <v>-1.120340272122477</v>
+        <v>0.9530912845304442</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.9617351711621649</v>
+        <v>1.466976151648421</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.882417423951371</v>
+        <v>0.358519323563153</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3.499062104387824</v>
+        <v>2.74903599965513</v>
       </c>
       <c r="D24" t="n">
-        <v>1.436576832128174</v>
+        <v>0.485660561432181</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4442644334617595</v>
+        <v>0.1089114998522537</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04395453941912893</v>
+        <v>2.176872900881533</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3440248902331074</v>
+        <v>0.0573312103389672</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -8560,46 +9890,46 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7997362733841766</v>
+        <v>0.739072506335564</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8446009110005764</v>
+        <v>0.7676144733305823</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.768231272849396</v>
+        <v>6.779167038804034</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7615699665042912</v>
+        <v>0.7615699657525096</v>
       </c>
       <c r="S24" t="n">
-        <v>0.099999997705382</v>
+        <v>0.2349397521222798</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3999999945149744</v>
+        <v>0.3999999948425383</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2600653486971247</v>
+        <v>0.5000000038259413</v>
       </c>
       <c r="V24" t="n">
-        <v>0.09999999851140819</v>
+        <v>0.1418761403960595</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7494379446507826</v>
+        <v>0.7015559889671873</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1038612926746863</v>
+        <v>0.1340653885591926</v>
       </c>
       <c r="Y24" t="n">
-        <v>3995.732300575364</v>
+        <v>2971.75640087489</v>
       </c>
       <c r="Z24" t="n">
         <v>-1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8446009110005764</v>
+        <v>0.7676144733305823</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.7615699665042912</v>
+        <v>0.7615699657525096</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -8610,66 +9940,66 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.7494379446507826</v>
+        <v>0.7015559889671873</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.634171133107276</v>
+        <v>3.685505794569735</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.0009095131654800735</v>
+        <v>0.001240177624749026</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.2657082127796765</v>
+        <v>0.06782580328461946</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.09780281237047755</v>
+        <v>2.320492249400389</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.02020165677570339</v>
+        <v>0.002547024957354649</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.768231272849396</v>
+        <v>6.779167038804034</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.5439516507863003</v>
+        <v>0.4391804271294646</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.1573288582270141</v>
+        <v>-0.3136671624273255</v>
       </c>
       <c r="AO24" t="n">
-        <v>-0.3523584537399462</v>
+        <v>-0.9629262611193901</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1.356996266372361</v>
+        <v>0.3378330730203389</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.4634101350452102</v>
+        <v>-1.241608889587855</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>16.02742566269002</v>
+        <v>6.693864711902439</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02815746213619474</v>
+        <v>0.08512832103909282</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6891588068984531</v>
+        <v>0.1540108718148722</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1013713092571047</v>
+        <v>8.728509814050597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01768046325080327</v>
+        <v>0.02172733661985029</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -8693,46 +10023,46 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8875683742703702</v>
+        <v>0.7390725070812486</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9345272009634895</v>
+        <v>0.7676144740993488</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.33751025132958</v>
+        <v>19.07718017297988</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5645967832243941</v>
+        <v>0.7615699655965384</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1854900228541271</v>
+        <v>0.2349397523017425</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3999999948263271</v>
+        <v>0.3999999947649425</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3116554712320814</v>
+        <v>0.5000000048246006</v>
       </c>
       <c r="V25" t="n">
-        <v>0.09999999951743914</v>
+        <v>0.1418761428230911</v>
       </c>
       <c r="W25" t="n">
-        <v>1.078291506409421</v>
+        <v>0.7015559896777094</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1090149001151575</v>
+        <v>0.1340653886701297</v>
       </c>
       <c r="Y25" t="n">
-        <v>59432.56015200894</v>
+        <v>42801.79845282505</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.9345272009634895</v>
+        <v>0.7676144740993488</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.5645967832243941</v>
+        <v>0.7615699655965384</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -8743,66 +10073,66 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.078291506409421</v>
+        <v>0.7015559896777094</v>
       </c>
       <c r="AF25" t="n">
-        <v>17.47228207721264</v>
+        <v>8.974155743064658</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.0002939850148222505</v>
+        <v>0.0002173827783864018</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.60206422231271</v>
+        <v>0.0959119203513549</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.1833041077279695</v>
+        <v>9.304373867609902</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.00127435265201832</v>
+        <v>0.0009652694978680744</v>
       </c>
       <c r="AK25" t="n">
-        <v>19.33751025132958</v>
+        <v>19.07718017297988</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.204863771245466</v>
+        <v>0.825676930688628</v>
       </c>
       <c r="AN25" t="n">
-        <v>-1.550406491217259</v>
+        <v>-1.069925931985848</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.1616806895399572</v>
+        <v>-0.8124486207054025</v>
       </c>
       <c r="AP25" t="n">
-        <v>-0.9940849443561461</v>
+        <v>0.9409401045558599</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-1.752506360101685</v>
+        <v>-1.66299350709844</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>9.061919909869614</v>
+        <v>0.4421104990239706</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0181665910343911</v>
+        <v>13.19732425925125</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09442424840067437</v>
+        <v>2.816777489164546</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1954170510066598</v>
+        <v>1.604404173315737</v>
       </c>
       <c r="G26" t="n">
-        <v>1.931138366967942</v>
+        <v>0.06314837069594158</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -8826,46 +10156,46 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9553165280177863</v>
+        <v>0.7390727277483335</v>
       </c>
       <c r="P26" t="n">
-        <v>1.026468194560592</v>
+        <v>0.7676147019429332</v>
       </c>
       <c r="Q26" t="n">
-        <v>10.69527831641379</v>
+        <v>4.795203833683704</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6837933699478116</v>
+        <v>0.7615699665269895</v>
       </c>
       <c r="S26" t="n">
-        <v>0.09999999776980481</v>
+        <v>0.2349404013063279</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3999999946589768</v>
+        <v>0.3999999944812534</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2247878180912749</v>
+        <v>0.5000000049949567</v>
       </c>
       <c r="V26" t="n">
-        <v>0.09999999867065287</v>
+        <v>0.141876332006719</v>
       </c>
       <c r="W26" t="n">
-        <v>0.86761500621457</v>
+        <v>0.7015561139306694</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1005400514018585</v>
+        <v>0.1340654986167144</v>
       </c>
       <c r="Y26" t="n">
-        <v>93080.9989149614</v>
+        <v>625.2741003041619</v>
       </c>
       <c r="Z26" t="n">
         <v>-1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.026468194560592</v>
+        <v>0.7676147019429332</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6837933699478116</v>
+        <v>0.7615699665269895</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -8876,66 +10206,66 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.86761500621457</v>
+        <v>0.7015561139306694</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.110858935378161</v>
+        <v>0.5927176449533305</v>
       </c>
       <c r="AG26" t="n">
-        <v>9.788097508173309e-05</v>
+        <v>0.03369099943938616</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.06404260227213419</v>
+        <v>1.754178606264762</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.5142945688583989</v>
+        <v>1.710255013687422</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1383693227154416</v>
+        <v>0.002805455408134527</v>
       </c>
       <c r="AK26" t="n">
-        <v>10.69527831641379</v>
+        <v>4.795203833683704</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.9572202195232169</v>
+        <v>-0.3544691715586477</v>
       </c>
       <c r="AN26" t="n">
-        <v>-1.740726560520908</v>
+        <v>1.120485887475754</v>
       </c>
       <c r="AO26" t="n">
-        <v>-1.024916463389384</v>
+        <v>0.4497525413255881</v>
       </c>
       <c r="AP26" t="n">
-        <v>-0.7090375448392141</v>
+        <v>0.2053137829815355</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.285813392297154</v>
+        <v>-1.19963785028506</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>88.01618808774326</v>
+        <v>0.2665249348337844</v>
       </c>
       <c r="D27" t="n">
-        <v>62.3765818947015</v>
+        <v>4.033641969154031</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8302283415310862</v>
+        <v>0.583593190474212</v>
       </c>
       <c r="F27" t="n">
-        <v>1.836692802030053</v>
+        <v>8.17333088184672</v>
       </c>
       <c r="G27" t="n">
-        <v>32.82145030831549</v>
+        <v>28.97718244313807</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -8956,119 +10286,119 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.167429548941</v>
+        <v>0.7390727277964448</v>
       </c>
       <c r="P27" t="n">
-        <v>1.201683162913394</v>
+        <v>0.7676147019904146</v>
       </c>
       <c r="Q27" t="n">
-        <v>94.27740552058215</v>
+        <v>11.43253038286904</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5443322679757407</v>
+        <v>0.7615699665264654</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1042937022573057</v>
+        <v>0.2349404012601182</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3999999945006344</v>
+        <v>0.3999999944747179</v>
       </c>
       <c r="U27" t="n">
-        <v>0.21470870152586</v>
+        <v>0.5000000049994059</v>
       </c>
       <c r="V27" t="n">
-        <v>0.09999999850074061</v>
+        <v>0.1418763322934327</v>
       </c>
       <c r="W27" t="n">
-        <v>1.076710298530744</v>
+        <v>0.7015561139733216</v>
       </c>
       <c r="X27" t="n">
-        <v>0.09626832900165394</v>
+        <v>0.1340654986155913</v>
       </c>
       <c r="Y27" t="n">
-        <v>279.0312390746425</v>
+        <v>846.0982872289621</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.201683162913394</v>
+        <v>0.7676147019904146</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5443322679757407</v>
+        <v>0.7615699665264654</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>fragile</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.076710298530744</v>
+        <v>0.7015561139733216</v>
       </c>
       <c r="AF27" t="n">
-        <v>84.73171352302323</v>
+        <v>0.3573179828197928</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.303663897289855</v>
+        <v>0.01029734715140867</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.749054987974078</v>
+        <v>0.3634389629386464</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.092819523766967</v>
+        <v>8.712567787808911</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.323443289997292</v>
+        <v>1.287352188176962</v>
       </c>
       <c r="AK27" t="n">
-        <v>94.27740552058215</v>
+        <v>11.43253038286904</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.944562555679924</v>
+        <v>-0.5742621541640669</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.795021572650338</v>
+        <v>0.6056973470940679</v>
       </c>
       <c r="AO27" t="n">
-        <v>-0.08080244518001445</v>
+        <v>-0.2338897842164331</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.2640365240032723</v>
+        <v>0.9123990808656299</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.516157767667171</v>
+        <v>1.462056155155667</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>64.6427018059547</v>
+        <v>0.5309351101535278</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6451914393738023</v>
+        <v>4.294096206681875</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03483154085585529</v>
+        <v>32.7055649293984</v>
       </c>
       <c r="F28" t="n">
-        <v>3.022421717195987</v>
+        <v>0.09809496344017229</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1675190230727432</v>
+        <v>2.697579830259134</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -9089,119 +10419,119 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.116916643982271</v>
+        <v>0.7358747056375252</v>
       </c>
       <c r="P28" t="n">
-        <v>1.116916643982271</v>
+        <v>0.7730510478240536</v>
       </c>
       <c r="Q28" t="n">
-        <v>71.63182999509672</v>
+        <v>21.28918165408557</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5396803948256202</v>
+        <v>0.7615699665296781</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1041913706454146</v>
+        <v>0.116717986979682</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3999999946175527</v>
+        <v>0.3999999944794566</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2147740497291313</v>
+        <v>0.2711586613917518</v>
       </c>
       <c r="V28" t="n">
-        <v>0.09999999868185457</v>
+        <v>0.09999999835909167</v>
       </c>
       <c r="W28" t="n">
-        <v>1.083333332647454</v>
+        <v>0.690131327348511</v>
       </c>
       <c r="X28" t="n">
-        <v>0.09610130538160445</v>
+        <v>0.1068444176183016</v>
       </c>
       <c r="Y28" t="n">
-        <v>14995.33429312562</v>
+        <v>1669.623164218233</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.116916643982271</v>
+        <v>0.7730510478240536</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5396803948256202</v>
+        <v>0.7615699665296781</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>fragile</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.083333332647454</v>
+        <v>0.690131327348511</v>
       </c>
       <c r="AF28" t="n">
-        <v>62.12248026946046</v>
+        <v>0.5672745263746249</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.004142787286705543</v>
+        <v>0.01176269040526402</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.03177035879404738</v>
+        <v>19.63926037415636</v>
       </c>
       <c r="AI28" t="n">
-        <v>8.377626308264126</v>
+        <v>0.2080100426385982</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01247693864392253</v>
+        <v>0.1727426931622109</v>
       </c>
       <c r="AK28" t="n">
-        <v>71.63182999509672</v>
+        <v>21.28918165408557</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.810519499915287</v>
+        <v>-0.2749585542938906</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.1903114036162812</v>
+        <v>0.6328717703198401</v>
       </c>
       <c r="AO28" t="n">
-        <v>-1.458027313069939</v>
+        <v>1.514621655183362</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.4803550611523</v>
+        <v>-1.008353290339657</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.7759358683500106</v>
+        <v>0.4309743057471738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>21.192957060738</v>
+        <v>5.830558109679524</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08766316016762059</v>
+        <v>35.37274159751259</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2282810469066574</v>
+        <v>57.4624343358206</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8441271699501433</v>
+        <v>38.44122193197017</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4349652711591156</v>
+        <v>0.1643575937684162</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -9222,119 +10552,119 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.117902051794015</v>
+        <v>0.7546223939910041</v>
       </c>
       <c r="P29" t="n">
-        <v>1.117902051794015</v>
+        <v>0.7836017703770652</v>
       </c>
       <c r="Q29" t="n">
-        <v>24.03009026403962</v>
+        <v>85.37983043642463</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5408765087816505</v>
+        <v>0.7615699665135085</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1033697394059942</v>
+        <v>0.221153409266387</v>
       </c>
       <c r="T29" t="n">
-        <v>0.399999994869712</v>
+        <v>0.3999999945488382</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2135764809520144</v>
+        <v>0.5000000049871816</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0999999990188386</v>
+        <v>0.2247824310798964</v>
       </c>
       <c r="W29" t="n">
-        <v>1.083333331531839</v>
+        <v>0.7165236392341808</v>
       </c>
       <c r="X29" t="n">
-        <v>0.09602236334006091</v>
+        <v>0.1341034216457866</v>
       </c>
       <c r="Y29" t="n">
-        <v>40668.55234143585</v>
+        <v>5657.382275324826</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.117902051794015</v>
+        <v>0.7836017703770652</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.5408765087816505</v>
+        <v>0.7615699665135085</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>fragile</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.083333331531839</v>
+        <v>0.7165236392341808</v>
       </c>
       <c r="AF29" t="n">
-        <v>20.34997823136494</v>
+        <v>7.818977926126136</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.0005003860983424043</v>
+        <v>0.0646625836237749</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.2076219448616802</v>
+        <v>35.7936955399092</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.354754456342681</v>
+        <v>40.97872733965374</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.03390191384013745</v>
+        <v>0.007243407877594924</v>
       </c>
       <c r="AK29" t="n">
-        <v>24.03009026403962</v>
+        <v>85.37983043642463</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.326191558200276</v>
+        <v>0.7657101280614271</v>
       </c>
       <c r="AN29" t="n">
-        <v>-1.057182877526212</v>
+        <v>1.548668721520392</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.6415301444254196</v>
+        <v>1.75938402047632</v>
       </c>
       <c r="AP29" t="n">
-        <v>-0.07359212085397715</v>
+        <v>1.584797184144205</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.3615454169443493</v>
+        <v>-0.784210225531051</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>89.20935767911</v>
+        <v>2.083710208720972</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01616092014366916</v>
+        <v>28.98014922862266</v>
       </c>
       <c r="E30" t="n">
-        <v>7.429333989108204</v>
+        <v>1.899083052130609</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2139741043792524</v>
+        <v>8.530541466329396</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4210722707598992</v>
+        <v>0.04906014442553373</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -9355,119 +10685,119 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.377103855530809</v>
+        <v>0.7546223960902997</v>
       </c>
       <c r="P30" t="n">
-        <v>1.377103855530809</v>
+        <v>0.7836017723073553</v>
       </c>
       <c r="Q30" t="n">
-        <v>93.83305640512151</v>
+        <v>13.84258198787505</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5491731252679101</v>
+        <v>0.7615699665266403</v>
       </c>
       <c r="S30" t="n">
-        <v>0.09999999770013378</v>
+        <v>0.221153407348591</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3999999945007257</v>
+        <v>0.3999999944724446</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2087990148187849</v>
+        <v>0.5000000049993008</v>
       </c>
       <c r="V30" t="n">
-        <v>0.09999999850053209</v>
+        <v>0.2247824400876461</v>
       </c>
       <c r="W30" t="n">
-        <v>1.083333332639759</v>
+        <v>0.716523640988932</v>
       </c>
       <c r="X30" t="n">
-        <v>0.09580882276984003</v>
+        <v>0.134103421630077</v>
       </c>
       <c r="Y30" t="n">
-        <v>2375706.749248032</v>
+        <v>4205.870458855159</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.377103855530809</v>
+        <v>0.7836017723073553</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.5491731252679101</v>
+        <v>0.7615699665266403</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>fragile</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.083333332639759</v>
+        <v>0.716523640988932</v>
       </c>
       <c r="AF30" t="n">
-        <v>85.47043539289116</v>
+        <v>2.794326686750043</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.597684580386221e-05</v>
+        <v>0.05297670244466143</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.625973223111042</v>
+        <v>1.182950241440008</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.6124940029689304</v>
+        <v>9.093642585326482</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.04078447666481171</v>
+        <v>0.002162130924926722</v>
       </c>
       <c r="AK30" t="n">
-        <v>93.83305640512151</v>
+        <v>13.84258198787505</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.950410412394576</v>
+        <v>0.3188373194717369</v>
       </c>
       <c r="AN30" t="n">
-        <v>-1.791533915718512</v>
+        <v>1.462100617470577</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.8709498826946742</v>
+        <v>0.2785439580457707</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.6696387827521937</v>
+        <v>0.9309765983862466</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.3756433576119891</v>
+        <v>-1.309271177631467</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>76.83856353774598</v>
+        <v>0.2474021140001688</v>
       </c>
       <c r="D31" t="n">
-        <v>10.8023949951404</v>
+        <v>29.59051462765532</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1238112825601379</v>
+        <v>0.07579834580915878</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2994937428456096</v>
+        <v>9.156619574847772</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4033789170429275</v>
+        <v>76.28118375658613</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -9488,95 +10818,1425 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7548305658560153</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.7838159010178805</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>16.32414572823105</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.76156996647908</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2217074847540164</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.3999999946274935</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.5000000049891441</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2250638486564479</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.285224520541978</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.1342029222135707</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>199.8967442689788</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.7838159010178805</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.76156996647908</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.285224520541978</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.3320208666063761</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.2999256916849148</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.05166453337423658</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>10.32757201568589</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4.027738100337651</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>16.32414572823105</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-0.6065965937340381</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.471152518320735</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-1.120340272122477</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.9617351711621649</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.882417423951371</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.499062104387824</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.436576832128174</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.4442644334617595</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.04395453941912893</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3440248902331074</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.7997362733841766</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.8446009110005764</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.768231272849396</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.7615699665042912</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.099999997705382</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.3999999945149744</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.2600653486971247</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.09999999851140819</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.7494379446507826</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1038612926746863</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>3995.732300575364</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.8446009110005764</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.7615699665042912</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.7494379446507826</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.634171133107276</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0009095131654800735</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.2657082127796765</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.09780281237047755</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.02020165677570339</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>4.768231272849396</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.5439516507863003</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.1573288582270141</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>-0.3523584537399462</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>-1.356996266372361</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-0.4634101350452102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>37</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6550595789833755</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.02089847824734005</v>
+      </c>
+      <c r="E33" t="n">
+        <v>47.85126936187322</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.04053147485742305</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.108293596298611</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8082604707876937</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8539841775274932</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>30.37365007086882</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.7615699665277879</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.09999999750720043</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3999999945913169</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.2356948212519741</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.09999999840901282</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.756242544027705</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.1033169421656713</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>139380.5042967549</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.8539841775274932</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.7615699665277879</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.756242544027705</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.6767875263689442</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.0002051742933903325</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>28.59729648147489</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.1010420797569419</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.2420762649469512</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>30.37365007086882</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.1837191982570747</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-1.679885336513072</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1.679893462897504</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-1.392207592883359</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.613661472582538</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.01312161903708897</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.07449348227690349</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.20763873910875</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42.99128608307436</v>
+      </c>
+      <c r="G34" t="n">
+        <v>59.22118257248598</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.9743006074141732</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.016605511278507</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>52.07815659593885</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.5376908912402081</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.2914549654284875</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3999999949854747</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.5000000049701842</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.1821898419872857</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.408895375723267</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.1277744364956107</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8059.258117237057</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.016605511278507</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.5376908912402081</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.408895375723267</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.0167660747837412</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.005845324102689949</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.1966403057741112</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>47.10897572248539</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>3.341033793069651</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>52.07815659593885</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-1.882012575364866</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-1.127881723694692</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>-0.6826916170488944</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.633380437218148</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.772477075454112</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9.061919909869614</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0181665910343911</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.09442424840067437</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1954170510066598</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.931138366967942</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9553165269985133</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.026468193785818</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>10.69527831522339</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.6837933708686902</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0999999975601196</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.3999999946291775</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.2247878180178422</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.09999999849367161</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.8676150055347496</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.1005400513964218</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>93080.99799101072</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.026468193785818</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.6837933708686902</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.8676150055347496</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>9.110858934885488</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>9.788097604803687e-05</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.06404260216535194</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.5142945690508326</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.1383693226109227</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>10.69527831522339</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.9572202195232169</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-1.740726560520908</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-1.024916463389384</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-0.7090375448392141</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.285813392297154</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>88.01618808774326</v>
+      </c>
+      <c r="D36" t="n">
+        <v>62.3765818947015</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8302283415310862</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.836692802030053</v>
+      </c>
+      <c r="G36" t="n">
+        <v>32.82145030831549</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.167429548941</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.201683162913394</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>94.27740552058215</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.5443322679757407</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.1042937022573057</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.3999999945006344</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.21470870152586</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.09999999850074061</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.076710298530744</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.09626832900165394</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>279.0312390746425</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.201683162913394</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.5443322679757407</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.076710298530744</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>84.73171352302323</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.303663897289855</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.749054987974078</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.092819523766967</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>2.323443289997292</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>94.27740552058215</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.944562555679924</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.795021572650338</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>-0.08080244518001445</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.2640365240032723</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.516157767667171</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>64.6427018059547</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.6451914393738023</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.03483154085585529</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.022421717195987</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1675190230727432</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>10</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.173976470596933</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.208494968548445</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>71.6318299863678</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.5396803945935512</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.1041913706284078</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.3999999944889326</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.2147740496573812</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.09999999835295273</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.083333332670561</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.09610130536305043</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14995.33423602986</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.208494968548445</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.5396803945935512</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.083333332670561</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>62.12248025746664</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.004142787301679653</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.03177035881100493</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>8.377626311443349</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.012476938674569</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>71.6318299863678</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.810519499915287</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-0.1903114036162812</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1.458027313069939</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.4803550611523</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>-0.7759358683500106</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>16.02742566269002</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.02815746213619474</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6891588068984531</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1013713092571047</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01768046325080327</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.207600258108835</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.254822053318313</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>17.34488294368279</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.548756805999245</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.09999999749911866</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.3999999945010851</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.2093206498764432</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.0999999983466104</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.083333332534641</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.09580553530929255</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>187251.4725871418</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.254822053318313</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.548756805999245</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.083333332534641</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>15.3551609524391</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>8.200288489209732e-05</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.6152334991039476</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.2893480222299764</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.001725134490235862</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>17.34488294368279</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.204863771245466</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-1.550406491217259</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>-0.1616806895399572</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-0.9940849443561461</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>-1.752506360101685</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>21.192957060738</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08766316016762059</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2282810469066574</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8441271699501433</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4349652711591156</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
         <v>0.6</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.377111284083251</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.377111284083251</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>75.73228764891769</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.5491727733395404</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.09999999766163428</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.3999999949239358</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.2087996887362319</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.09999999842577559</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.083333332640151</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.09580882459726055</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3061.302104446599</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="O39" t="n">
+        <v>1.117902051794015</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.117902051794015</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>24.03009026403962</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.5408765087816505</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.1033697394059942</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.399999994869712</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.2135764809520144</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.0999999990188386</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.083333331531839</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.09602236334006091</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>40668.55234143585</v>
+      </c>
+      <c r="Z39" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AA31" t="n">
-        <v>1.377111284083251</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.5491727733395404</v>
-      </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AA39" t="n">
+        <v>1.117902051794015</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.5408765087816505</v>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>fragile</t>
         </is>
       </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.083333332640151</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>73.61812456293364</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.0240479776419328</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.1104232112752492</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.8572880687983905</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.03907049562832649</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>75.73228764891769</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.083333331531839</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>20.34997823136494</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.0005003860983424043</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.2076219448616802</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.354754456342681</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.03390191384013745</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>24.03009026403962</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.326191558200276</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-1.057182877526212</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-0.6415301444254196</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-0.07359212085397715</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>-0.3615454169443493</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>89.20935767911</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01616092014366916</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7.429333989108204</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2139741043792524</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4210722707598992</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.377103859023908</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.377103859023908</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>93.83305639194438</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.5491731255894229</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.0999999975003934</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.3999999945276524</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.208799015126044</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.09999999836445793</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.083333332584748</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.09580882276109781</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2375706.478017149</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.377103859023908</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.5491731255894229</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.083333332584748</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>85.4704353850923</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.597684990800254e-05</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>6.625973218147726</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.6124940019417454</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.04078447732796903</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>93.83305639194438</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.950410412394576</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-1.791533915718512</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.8709498826946742</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-0.6696387827521937</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-0.3756433576119891</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>76.83856353774598</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10.8023949951404</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1238112825601379</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2994937428456096</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.4033789170429275</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.37711128055112</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.37711128055112</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>75.73228763606222</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.5491727738003297</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.09999999748976168</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.3999999944689408</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.2087996885615724</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.09999999832143</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.083333332640155</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.09580882458046941</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3061.302248515653</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.37711128055112</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.5491727738003297</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.083333332640155</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>73.61812455003158</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.02404797650598764</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.1104232111557526</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.8572880696147496</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.03907049611401094</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>75.73228763606222</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
         <v>1.885579237326283</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AN41" t="n">
         <v>1.033520053437076</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AO41" t="n">
         <v>-0.9072397775263723</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AP41" t="n">
         <v>-0.5236122466503326</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ41" t="n">
         <v>-0.3942868043165935</v>
       </c>
     </row>
